--- a/salida/v10/Layout_v10_zonas_y_equipos.xlsx
+++ b/salida/v10/Layout_v10_zonas_y_equipos.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>736.1</v>
+        <v>691.1</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>20.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="10">
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>248.4</v>
+        <v>205.5</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="11">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>238.9</v>
+        <v>326.8</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="13">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="F45" s="5" t="n">
         <v>20</v>
@@ -2907,13 +2907,13 @@
         <v>25</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J45" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="L45" s="4" t="n">
         <v>35</v>
@@ -2980,12 +2980,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>C-03W</t>
+          <t>C-03E</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Franja entre el corte y el cilindrado</t>
+          <t>Paso de los carros del marcado al cilindrado</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2999,42 +2999,46 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>21.3</v>
+        <v>24.8</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>20</v>
+        <v>26.4</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>21.8</v>
+        <v>28.8</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>2.5</v>
+        <v>10.4</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR 2.1: los carros llenos esperan al costado de la mesa de marcado</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>C-03E</t>
+          <t>C-05</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Paso de los carros del marcado al cilindrado</t>
+          <t>5 Soldadura longitudinal</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3048,46 +3052,44 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>24.8</v>
+        <v>29.3</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>26.4</v>
+        <v>20</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>28.8</v>
+        <v>35.3</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I48" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>2.6</v>
-      </c>
       <c r="K48" s="5" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>22</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 2.1: los carros llenos esperan al costado de la mesa de marcado</t>
+          <t>W-CAR, tabla de espacios del puesto 5: ≈ 5,5 × 4,0 m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>C-05</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>5 Soldadura longitudinal</t>
+          <t>4 Punteo del cuerpo</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3104,41 +3106,41 @@
         <v>29.3</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>20</v>
+        <v>24.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>34.8</v>
+        <v>35.3</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 5: ≈ 5,5 × 4,0 m</t>
+          <t>W-CAR, tabla de espacios del puesto 4: ≈ 6,0 × 4,5 m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>C-45</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>4 Punteo del cuerpo</t>
+          <t>Cortina de soldadura entre 3 y 4/5</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3152,44 +3154,46 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" s="5" t="n">
         <v>29.3</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>35.3</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>29</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J50" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K50" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="K50" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>27</v>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 4: ≈ 6,0 × 4,5 m</t>
+          <t>W-CAR 4: cortina de soldadura</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>C-45</t>
+          <t>C-45b</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Cortina de soldadura entre 3 y 4/5</t>
+          <t>Cortina de soldadura entre 4 y 5</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -3203,25 +3207,25 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>29.3</v>
+        <v>35.3</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>29</v>
+        <v>24.5</v>
       </c>
       <c r="I51" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J51" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="J51" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="K51" s="5" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -3237,12 +3241,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>C-45b</t>
+          <t>C-07</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Cortina de soldadura entre 4 y 5</t>
+          <t>7 Armado y soldadura circunferencial</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3256,13 +3260,13 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>29.3</v>
+        <v>36.8</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>35.3</v>
+        <v>42.8</v>
       </c>
       <c r="H52" s="5" t="n">
         <v>24.5</v>
@@ -3271,31 +3275,29 @@
         <v>6</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>27</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 4: cortina de soldadura</t>
+          <t>W-CAR, tabla de espacios del puesto 7: ≈ 6,0 × 4,5 m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>C-45c</t>
+          <t>C-06</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Franja al este de la soldadura longitudinal</t>
+          <t>6 Soldadura de cupla en la cúpula</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3309,42 +3311,44 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>34.8</v>
+        <v>36.8</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>35.3</v>
+        <v>42.8</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR, tabla de espacios del puesto 6: ≈ 4,5 × 3,5 m</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>C-07</t>
+          <t>C-67</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>7 Armado y soldadura circunferencial</t>
+          <t>Paso del carro canasto de cúpulas de 6 a 7</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -3361,41 +3365,43 @@
         <v>36.8</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>20</v>
+        <v>24.5</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>42.8</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>6</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v>27</v>
+        <v>6</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 7: ≈ 6,0 × 4,5 m</t>
+          <t>W-CAR 6 y 7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>C-06</t>
+          <t>C-08</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>6 Soldadura de cupla en la cúpula</t>
+          <t>8 Soldadura de accesorios</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3409,44 +3415,44 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>36.8</v>
+        <v>43.3</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>41.3</v>
+        <v>49.8</v>
       </c>
       <c r="H55" s="5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="L55" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="I55" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 6: ≈ 4,5 × 3,5 m</t>
+          <t>W-CAR, tabla de espacios del puesto 8: ≈ 6,5 × 4,5 m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>C-67</t>
+          <t>C-081</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Paso del carro canasto de cúpulas de 6 a 7</t>
+          <t>8.1 Fabricación de accesorios</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3460,46 +3466,44 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>36.8</v>
+        <v>43.3</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>42.8</v>
+        <v>51.3</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>25.5</v>
+        <v>29</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>32</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 6 y 7</t>
+          <t>W-CAR, tabla de espacios del puesto 8.1: ≈ 8,0 × 4,0 m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>C-67b</t>
+          <t>C-78</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Franja al este de la cupla</t>
+          <t>Cortina de soldadura entre 7 y 8</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3513,42 +3517,46 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>41.3</v>
+        <v>42.8</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>42.8</v>
+        <v>43.3</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>29</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M57" s="4" t="inlineStr"/>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR 8: cortina de soldadura</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>C-08</t>
+          <t>C-88</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>8 Soldadura de accesorios</t>
+          <t>Cortina entre 8 y 8.1</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3565,41 +3573,43 @@
         <v>43.3</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>20</v>
+        <v>24.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>49.8</v>
+        <v>51.3</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="L58" s="4" t="n">
-        <v>29</v>
+        <v>4</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 8: ≈ 6,5 × 4,5 m</t>
+          <t>W-CAR 8: cortina de soldadura</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>C-081</t>
+          <t>C-08E</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>8.1 Fabricación de accesorios</t>
+          <t>Salida de los carros sobre su juego provisorio</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3613,44 +3623,46 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>43.3</v>
+        <v>49.8</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G59" s="5" t="n">
         <v>51.3</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>29</v>
+        <v>24.5</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v>32</v>
+        <v>6.75</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 8.1: ≈ 8,0 × 4,0 m</t>
+          <t>W-CAR 8: salida demarcada en amarillo</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>C-78</t>
+          <t>C-10</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Cortina de soldadura entre 7 y 8</t>
+          <t>10 Secado</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3664,46 +3676,44 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>42.8</v>
+        <v>51.3</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>20</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>43.3</v>
+        <v>54.8</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>29</v>
+        <v>22.5</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.75</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>7.5</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 8: cortina de soldadura</t>
+          <t>W-CAR, tabla de espacios del puesto 10: ≈ 3,0 × 2,5 m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>C-88</t>
+          <t>C-09</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Cortina entre 8 y 8.1</t>
+          <t>9 Prueba hidráulica</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3717,46 +3727,44 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>43.3</v>
+        <v>51.3</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>51.3</v>
+        <v>57.3</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>22</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 8: cortina de soldadura</t>
+          <t>W-CAR, tabla de espacios del puesto 9: ≈ 5,5 × 4,0 m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>C-08E</t>
+          <t>C-910a</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Salida de los carros sobre su juego provisorio</t>
+          <t>Paso de la prueba hidráulica al secado</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3770,25 +3778,25 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>49.8</v>
+        <v>51.3</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>51.3</v>
+        <v>57.3</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>6.75</v>
+        <v>15</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -3797,19 +3805,19 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 8: salida demarcada en amarillo</t>
+          <t>W-CAR 9 y 10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>C-10</t>
+          <t>C-910c</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>10 Secado</t>
+          <t>Salida del secado hacia el pulmón de despacho</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3823,49 +3831,51 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>51.8</v>
+        <v>54.8</v>
       </c>
       <c r="F63" s="5" t="n">
         <v>20</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>54.8</v>
+        <v>57.3</v>
       </c>
       <c r="H63" s="5" t="n">
         <v>22.5</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J63" s="5" t="n">
         <v>2.5</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 10: ≈ 3,0 × 2,5 m</t>
+          <t>W-CAR 10: los carros secos van al puesto 11, al otro lado del pasillo</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>C-09</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>9 Prueba hidráulica</t>
+          <t>4 Corte de disco y embutido (desbobinador, alimentador y prensa)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Carros 25 a 100 kg</t>
+          <t>Manuales 1 a 10 kg</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3874,49 +3884,49 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>51.3</v>
+        <v>15.4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>57.3</v>
+        <v>25.4</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J64" s="5" t="n">
         <v>4</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="L64" s="4" t="n">
-        <v>22</v>
+        <v>40</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>26</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 9: ≈ 5,5 × 4,0 m</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>C-910a</t>
+          <t>M-PCU</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Paso de la prueba hidráulica al secado</t>
+          <t>Zona de cúpulas (5 carros de 12 cajones), al lado del numerado</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Carros 25 a 100 kg</t>
+          <t>Manuales 1 a 10 kg</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3925,25 +3935,25 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>51.3</v>
+        <v>25.4</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>22.5</v>
+        <v>41</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>57.3</v>
+        <v>28.3</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -3952,24 +3962,24 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 9 y 10</t>
+          <t>W-MAN 3: 3 a 5 carros, al lado del numerado y la soldadura de cuello</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>C-910b</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Franja junto al secado (lado oeste)</t>
+          <t>6 Numerado de cúpula (pegado a la soldadura de cuello)</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Carros 25 a 100 kg</t>
+          <t>Manuales 1 a 10 kg</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3978,47 +3988,49 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>51.3</v>
+        <v>28.3</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>51.8</v>
+        <v>30.9</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>22.5</v>
+        <v>45</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="4" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 6: la cúpula pasa a mano a la soldadura de cuello de al lado</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>C-910c</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Salida del secado hacia el pulmón de despacho</t>
+          <t>7 Soldadura del cuello a la cúpula</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Carros 25 a 100 kg</t>
+          <t>Manuales 1 a 10 kg</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -4027,46 +4039,44 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>54.8</v>
+        <v>30.9</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>57.3</v>
+        <v>33.4</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>22.5</v>
+        <v>45</v>
       </c>
       <c r="I67" s="5" t="n">
         <v>2.5</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>5.3</v>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 10: los carros secos van al puesto 11, al otro lado del pasillo</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>4 Corte de disco y embutido (desbobinador, alimentador y prensa)</t>
+          <t>5 Preparación de cuello (2 prensas de banco)</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4080,28 +4090,28 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>15.4</v>
+        <v>33.4</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>41</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>25.4</v>
+        <v>35.3</v>
       </c>
       <c r="H68" s="5" t="n">
         <v>45</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>10</v>
+        <v>1.9</v>
       </c>
       <c r="J68" s="5" t="n">
         <v>4</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>26</v>
+        <v>4.5</v>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
@@ -4112,12 +4122,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>M-PCU</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Zona de cúpulas (5 carros de 12 cajones), al lado del numerado</t>
+          <t>3 Corte de tubo 1 kg (láser Leapion, orientado norte-sur)</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -4131,46 +4141,44 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>25.4</v>
+        <v>15.4</v>
       </c>
       <c r="F69" s="5" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H69" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="G69" s="5" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>45</v>
-      </c>
       <c r="I69" s="5" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>4</v>
+        <v>13.6</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>35.36</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>25.5</v>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 3: 3 a 5 carros, al lado del numerado y la soldadura de cuello</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>M-PT</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>6 Numerado de cúpula (pegado a la soldadura de cuello)</t>
+          <t>Tramos 1 kg: carros «en consumo» y «lleno» al lado del encastre</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -4184,44 +4192,46 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>28.3</v>
+        <v>18</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>30.9</v>
+        <v>21</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J70" s="5" t="n">
         <v>4</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>2.3</v>
+        <v>12</v>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 6: la cúpula pasa a mano a la soldadura de cuello de al lado</t>
+          <t>W-MAN 2: al lado del encastre se demarcan dos posiciones de carro de 1,2 × 0,8 m, «en consumo» y «lleno»</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>7 Soldadura del cuello a la cúpula</t>
+          <t>10 Encastre de fondo y zona de fondos (5 carros)</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -4235,44 +4245,44 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>30.9</v>
+        <v>21</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>33.4</v>
+        <v>26.6</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="J71" s="5" t="n">
         <v>4</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>10</v>
+        <v>22.4</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>5 Preparación de cuello (2 prensas de banco)</t>
+          <t>11 Bordoneado</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -4286,28 +4296,28 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>33.4</v>
+        <v>26.6</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>35.3</v>
+        <v>31</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J72" s="5" t="n">
         <v>4</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>7.6</v>
+        <v>17.6</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
@@ -4318,12 +4328,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-PB</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>3 Corte de tubo 1 kg (láser Leapion, orientado norte-sur)</t>
+          <t>Pulmones del bordoneado a la soldadura circunferencial</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -4337,44 +4347,46 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>15.4</v>
+        <v>31</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>27.4</v>
+        <v>35</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>18</v>
+        <v>35.3</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>13.6</v>
+        <v>4</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>25.5</v>
+        <v>17.2</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
+          <t>W-MAN 9 y 10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>M-PT</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Tramos 1 kg: carros «en consumo» y «lleno» al lado del encastre</t>
+          <t>8 Cilindrado</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -4391,43 +4403,41 @@
         <v>18</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>21</v>
+        <v>23.4</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="J74" s="5" t="n">
         <v>4</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.6</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>7.3</v>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 2: al lado del encastre se demarcan dos posiciones de carro de 1,2 × 0,8 m, «en consumo» y «lleno»</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>10 Encastre de fondo y zona de fondos (5 carros)</t>
+          <t>9 Soldadura longitudinal</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -4441,44 +4451,44 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>21</v>
+        <v>23.4</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>26.6</v>
+        <v>29.4</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J75" s="5" t="n">
         <v>4</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 3</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>M-PV</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>11 Bordoneado</t>
+          <t>Cuerpos soldados y cambio de formato</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -4492,44 +4502,46 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>26.6</v>
+        <v>29.4</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>31</v>
+        <v>35.3</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="J76" s="5" t="n">
         <v>4</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>3.6</v>
+        <v>23.6</v>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
+          <t>W-MAN 7: PU-V2, PU-V3, PU-FX</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>M-PB</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Pulmones del bordoneado a la soldadura circunferencial</t>
+          <t>12 Soldadura circunferencial (2 máquinas)</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -4543,46 +4555,44 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>31</v>
+        <v>36.8</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>35</v>
+        <v>40.5</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>35.3</v>
+        <v>43.8</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>31.5</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>17.5</v>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 9 y 10</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>8 Cilindrado</t>
+          <t>13 Control de espesor</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -4596,44 +4606,44 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>18</v>
+        <v>36.8</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>23.4</v>
+        <v>43.8</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>33</v>
+        <v>40.5</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>21.6</v>
+        <v>17.5</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 12: PU-S y 2 PU-RT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-14</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>9 Soldadura longitudinal</t>
+          <t>14 Prueba hidráulica (2 bancos)</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -4647,44 +4657,44 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>23.4</v>
+        <v>36.8</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>29</v>
+        <v>33.5</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>29.4</v>
+        <v>43.8</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>24</v>
+        <v>31.5</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>8.4</v>
+        <v>14.1</v>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 13: 2 PU-6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>M-PV</t>
+          <t>M-15</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Cuerpos soldados y cambio de formato</t>
+          <t>15 Secado (4 secadoras)</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4698,46 +4708,44 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>29.4</v>
+        <v>36.8</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>29</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>35.3</v>
+        <v>43.8</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>31.5</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 7: PU-V2, PU-V3, PU-FX</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 14: 2 PU-7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>M-16</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>12 Soldadura circunferencial (2 máquinas)</t>
+          <t>16 Granallado</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -4751,28 +4759,28 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>36.8</v>
+        <v>45.3</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>40.5</v>
+        <v>29</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>43.8</v>
+        <v>51.8</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>17.5</v>
+        <v>27.4</v>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
@@ -4783,12 +4791,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>M-17</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>13 Control de espesor</t>
+          <t>17 y 18 Detección y corrección de defectos</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -4802,44 +4810,44 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>36.8</v>
+        <v>51.8</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>43.8</v>
+        <v>57.3</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>40.5</v>
+        <v>34</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 12: PU-S y 2 PU-RT</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 16 y 17 (3 jaulas y carro de corregibles)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>M-14</t>
+          <t>M-18</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>14 Prueba hidráulica (2 bancos)</t>
+          <t>19 Cuelgue en el riel de la pintura</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -4853,49 +4861,51 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>36.8</v>
+        <v>58.8</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>33.5</v>
+        <v>29</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>43.8</v>
+        <v>66</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>14.1</v>
+        <v>36</v>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 13: 2 PU-6</t>
+          <t>W-MAN 18: carga de la línea; carros móviles y ganchos por formato</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>M-15</t>
+          <t>RV-M</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>15 Secado (4 secadoras)</t>
+          <t>Reserva de ampliación de manuales (junto a la columna de puestos saturados)</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Manuales 1 a 10 kg</t>
+          <t>Libre / reserva</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4904,49 +4914,51 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>36.8</v>
+        <v>45.3</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>43.8</v>
+        <v>57.3</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>33.5</v>
+        <v>45</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>6</v>
+        <v>132</v>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 14: 2 PU-7</t>
+          <t>Lugar para la máquina siguiente de los puestos saturados en 2035. X-MAN 2035, aprovechamiento: sold. longitudinal 97 %, encastre, sold. circunferencial y prueba hidráulica 94 %, secado, preparación de cuello y etiquetado 92 %</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>M-16</t>
+          <t>RV-T</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>16 Granallado</t>
+          <t>Reserva de la pintura y del granallado</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Manuales 1 a 10 kg</t>
+          <t>Libre / reserva</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4955,49 +4967,51 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>45.3</v>
+        <v>58.8</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>51.8</v>
+        <v>66</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>27.4</v>
+        <v>79.2</v>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10</t>
+          <t>X-MAN 2035, aprovechamiento: sold. longitudinal 97 %, encastre, sold. circunferencial y prueba hidráulica 94 %, secado, preparación de cuello y etiquetado 92 %</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>M-19</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>17 y 18 Detección y corrección de defectos</t>
+          <t>19 Pintura en polvo + horno (línea Firesafer)</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Manuales 1 a 10 kg</t>
+          <t>Pintura</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -5006,49 +5020,49 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>51.8</v>
+        <v>66</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>57.3</v>
+        <v>76</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>270</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>270</v>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10; W-MAN 16 y 17 (3 jaulas y carro de corregibles)</t>
+          <t>ET: 25000 × 8000 × 4000 mm; W-MAN 18 y X-MAN 19; franja de servicio de 1 m</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>M-18</t>
+          <t>M-20</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>19 Cuelgue en el riel de la pintura</t>
+          <t>20 a 25 Terminación: carga, ensamblaje, presurización, pérdidas, etiquetado y embalaje</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Manuales 1 a 10 kg</t>
+          <t>Terminación de manuales</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -5060,48 +5074,46 @@
         <v>58.8</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G87" s="5" t="n">
         <v>66</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I87" s="5" t="n">
         <v>7.2</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>64.8</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>47</v>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 18: carga de la línea; carros móviles y ganchos por formato</t>
+          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10 (Guerchet de los puestos 20 a 25: 42,4 m² + 6 carros pulmón)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>RV-M</t>
+          <t>C-16</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Reserva de ampliación de manuales (junto a la columna de puestos saturados)</t>
+          <t>16 Depósito de PT de carros: retenidos (amarillo) y liberados (verde)</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Libre / reserva</t>
+          <t>Depósitos de producto terminado</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -5110,46 +5122,44 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>45.3</v>
+        <v>24.7</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>34</v>
+        <v>3.5</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>57.3</v>
+        <v>39.7</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>45</v>
+        <v>10.2</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>11</v>
+        <v>6.7</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>100.5</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>72</v>
       </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>Lugar para la máquina siguiente de los puestos saturados en 2035. X-MAN 2035, aprovechamiento: sold. longitudinal 97 %, encastre, sold. circunferencial y prueba hidráulica 94 %, secado, preparación de cuello y etiquetado 92 %</t>
+          <t>W-CAR, tabla de espacios del puesto 16: 0,5 m² por carro y los pasillos; 74 retenidos y 70 liberados (demanda 2035), paso de carros al norte</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>RV-T</t>
+          <t>RV-C1</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Reserva de la pintura y del granallado</t>
+          <t>Libre (reserva del depósito de PT de carros)</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -5163,25 +5173,25 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>58.8</v>
+        <v>24.7</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>34</v>
+        <v>10.2</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>66</v>
+        <v>37.7</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>45</v>
+        <v>13.5</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>11</v>
+        <v>3.3</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>79.2</v>
+        <v>42.9</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -5190,24 +5200,24 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>X-MAN 2035, aprovechamiento: sold. longitudinal 97 %, encastre, sold. circunferencial y prueba hidráulica 94 %, secado, preparación de cuello y etiquetado 92 %</t>
+          <t>Lo que no ocupa la demanda 2035 en el depósito 16 (W-CAR pedía ≈ 200 m² para 20 carros por día)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>M-19</t>
+          <t>C-16A</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>19 Pintura en polvo + horno (línea Firesafer)</t>
+          <t>16 Entrada de los cilindros pintados desde el pasillo principal</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Pintura</t>
+          <t>Depósitos de producto terminado</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -5216,49 +5226,51 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>66</v>
+        <v>37.7</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>20</v>
+        <v>10.2</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>76</v>
+        <v>39.7</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>47</v>
+        <v>13.5</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>27</v>
+        <v>3.3</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>270</v>
-      </c>
-      <c r="L90" s="4" t="n">
-        <v>270</v>
+        <v>6.6</v>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>ET: 25000 × 8000 × 4000 mm; W-MAN 18 y X-MAN 19; franja de servicio de 1 m</t>
+          <t>Paso de carros a mano (criterio): los cilindros vendidos vacíos vienen del puesto 12 por C-11A y el pasillo principal</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>M-20</t>
+          <t>C-16P</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>20 a 25 Terminación: carga, ensamblaje, presurización, pérdidas, etiquetado y embalaje</t>
+          <t>16 Pasillo de despacho (P2) y rechazados (rojo)</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Terminación de manuales</t>
+          <t>Depósitos de producto terminado</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -5267,49 +5279,49 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>20</v>
+        <v>24.7</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>66</v>
+        <v>39.7</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>29</v>
+        <v>3.5</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>64.8</v>
+        <v>52.5</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>47</v>
+        <v>11.5</v>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>W-MAN; máquina de X-MAN; medida de la tabla de áreas v10 (Guerchet de los puestos 20 a 25: 42,4 m² + 6 carros pulmón)</t>
+          <t>W-CAR 16: pasillo entre las zonas y la puerta; rechazados: 23 carros a 0,5 m²</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>C-16</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>16 Depósito de PT de carros: retenidos (amarillo) y liberados (verde)</t>
+          <t>17 Ensayos de lote (recinto de descarga, balanza y mesa)</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Depósitos de producto terminado</t>
+          <t>Carros 25 a 100 kg</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -5318,95 +5330,95 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>3.5</v>
+        <v>39.7</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>39.7</v>
+        <v>55.2</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>150</v>
+        <v>69.75</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 16: retenidos ≈ 9 × 10 m (180 carros), liberados ≈ 6 × 10 m (100 carros), pasillo hasta la puerta</t>
+          <t>W-CAR, tabla de espacios del puesto 17: ≈ 15,5 × 4,5 m (el patio de rodadura va afuera)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>C-16P</t>
+          <t>C-14</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>16 Pasillo de despacho (P2) y rechazados (rojo)</t>
+          <t>14 Sala del ensayo de pérdidas (paneles aislantes, split)</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Depósitos de producto terminado</t>
+          <t>Carros 25 a 100 kg</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="F93" s="4" t="n">
-        <v>0</v>
+        <v>39.7</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>4.5</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>39.7</v>
+        <v>43.7</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="L93" s="4" t="n">
-        <v>50</v>
+        <v>16</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>14.16666666666667</v>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16: pasillo del autoelevador entre las zonas y la puerta; rechazados ≈ 5 × 3 m</t>
+          <t>W-CAR 14: 25 m² para 30 lugares; con los 17 de 2035, a la misma relación</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>C-17</t>
+          <t>C-15</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>17 Ensayos de lote (recinto de descarga, balanza y mesa)</t>
+          <t>15 Etiquetado e inspección final</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -5422,42 +5434,42 @@
       <c r="E94" s="5" t="n">
         <v>39.7</v>
       </c>
-      <c r="F94" s="4" t="n">
-        <v>0</v>
+      <c r="F94" s="5" t="n">
+        <v>8.5</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>55.2</v>
+        <v>43.7</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>69.75</v>
+        <v>20</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 17: ≈ 15,5 × 4,5 m (el patio de rodadura va afuera)</t>
+          <t>W-CAR, tabla de espacios del puesto 15: ≈ 3,5 × 2,5 m, más el paso de los carros al depósito 16</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>C-14</t>
+          <t>C-13</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>14 Sala del ensayo de pérdidas (paneles aislantes, split)</t>
+          <t>13 Carga, armado y presurización</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -5467,48 +5479,48 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>area</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>39.7</v>
+        <v>43.7</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>44.7</v>
+        <v>55.2</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>25</v>
+        <v>74.75</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 14: 5,0 × 5,0 m, 30 lugares numerados</t>
+          <t>W-CAR, tabla de espacios del puesto 13: ≈ 10 × 6 m</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>C-15</t>
+          <t>C-1314</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>15 Etiquetado e inspección final</t>
+          <t>Paso de la carga a la sala de pérdidas y a los ensayos</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -5522,44 +5534,46 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>39.7</v>
+        <v>43.7</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>44.7</v>
+        <v>55.2</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="L96" s="4" t="n">
-        <v>9</v>
+        <v>28.75</v>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 15: ≈ 3,5 × 2,5 m, más el paso de los carros al depósito 16</t>
+          <t>W-CAR 13, 14 y 17: recorrido de los carros de la muestra; estanterías del puesto 13</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>C-13</t>
+          <t>C-12</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>13 Carga, armado y presurización</t>
+          <t>12 Pulmón de pintados (49 carros), al lado del puesto 13</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -5573,49 +5587,49 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>44.7</v>
+        <v>55.2</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>55.2</v>
+        <v>61.40000000000001</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>68.25</v>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v>60</v>
+        <v>32.86</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>24.5</v>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 13: ≈ 10 × 6 m</t>
+          <t>W-CAR 12: filas por modelo y lote, al lado del puesto 13; 49 carros a 0,5 m²</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>C-1314</t>
+          <t>RV-C2</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Paso de la carga a la sala de pérdidas y a los ensayos</t>
+          <t>Libre (reserva del pulmón de pintados)</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Carros 25 a 100 kg</t>
+          <t>Libre / reserva</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -5624,25 +5638,25 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>44.7</v>
+        <v>55.2</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>55.2</v>
+        <v>61.40000000000001</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>26.25</v>
+        <v>30.38</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -5651,19 +5665,19 @@
       </c>
       <c r="M98" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 13, 14 y 17: recorrido de los carros de la muestra; estanterías del puesto 13</t>
+          <t>Lo que no ocupa la demanda 2035 en el pulmón 12 (W-CAR: 120 carros para 20 por día)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>C-12</t>
+          <t>C-12C</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>12 Pulmón de pintados (120 carros), al lado del puesto 13</t>
+          <t>12 Recepción de pintados: cambio de juego y rechazados del pintor (P6)</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -5679,23 +5693,23 @@
       <c r="E99" s="5" t="n">
         <v>55.2</v>
       </c>
-      <c r="F99" s="5" t="n">
-        <v>3.3</v>
+      <c r="F99" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>61.40000000000001</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>13.5</v>
+        <v>3.3</v>
       </c>
       <c r="I99" s="5" t="n">
         <v>6.2</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>10.2</v>
+        <v>3.3</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>63.24</v>
+        <v>20.46</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -5704,19 +5718,19 @@
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 12: pulmón de pintados ≈ 10 × 7 m, filas por modelo y lote; el puesto 12 (con C-12C) ≈ 79 m²</t>
+          <t>W-CAR 12: 2 lugares de cambio de juego de 2,0 × 1,5 m y rechazados ≈ 2 × 1,5 m, al lado de la puerta</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>C-12C</t>
+          <t>C-11A</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>12 Recepción de pintados: cambio de juego y rechazados del pintor (P6)</t>
+          <t>11 Pasillo de los carros a la puerta (secos, cilindros pintados)</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -5730,25 +5744,25 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="F100" s="4" t="n">
-        <v>0</v>
+        <v>61.40000000000001</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>2.25</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>61.40000000000001</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>3.3</v>
+        <v>13.5</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>3.3</v>
+        <v>11.25</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>20.46</v>
+        <v>11.25</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -5757,19 +5771,19 @@
       </c>
       <c r="M100" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 12: 2 lugares de cambio de juego de 2,0 × 1,5 m y rechazados ≈ 2 × 1,5 m, al lado de la puerta</t>
+          <t>W-CAR 11: pasillo ≈ 1 m entre las filas y la puerta; por acá suben los cilindros pintados al pasillo principal</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>C-11A</t>
+          <t>C-11</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>11 Pasillo de los carros a la puerta</t>
+          <t>11 Pulmón de despacho a la pintura tercerizada (84 carros)</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -5783,51 +5797,49 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>61.40000000000001</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="F101" s="5" t="n">
         <v>2.25</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>62.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>13.5</v>
+        <v>10.7</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>11.25</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>43.94</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>42</v>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 11: pasillo ≈ 10 × 1 m entre las filas y la puerta</t>
+          <t>W-CAR, tabla de espacios del puesto 11: filas por modelo y semana, demarcadas en amarillo; 84 carros a 0,5 m²</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>C-11</t>
+          <t>RV-C3</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>11 Pulmón de despacho a la pintura tercerizada (120 carros)</t>
+          <t>Libre (reserva del pulmón de despacho)</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Carros 25 a 100 kg</t>
+          <t>Libre / reserva</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5839,7 +5851,7 @@
         <v>62.40000000000001</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>2.25</v>
+        <v>10.7</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>67.59999999999999</v>
@@ -5851,17 +5863,19 @@
         <v>5.2</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>11.25</v>
+        <v>2.8</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="L102" s="4" t="n">
-        <v>57</v>
+        <v>14.56</v>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 11: filas por modelo y semana ≈ 10 × 6 m, demarcadas en amarillo</t>
+          <t>Lo que no ocupa la demanda 2035 en el pulmón 11 (W-CAR: 120 carros para 20 por día)</t>
         </is>
       </c>
     </row>
@@ -19227,7 +19241,7 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Pulmón de despacho: 15 filas de 8 carros por modelo y semana (120)</t>
+          <t>Pulmón de despacho: 11 filas de 8 carros por modelo y semana (84)</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -19244,19 +19258,19 @@
         <v>62.45</v>
       </c>
       <c r="F219" s="5" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="G219" s="5" t="n">
         <v>67.55</v>
       </c>
       <c r="H219" s="5" t="n">
-        <v>12.75</v>
+        <v>10.1</v>
       </c>
       <c r="I219" s="5" t="n">
         <v>5.1</v>
       </c>
       <c r="J219" s="5" t="n">
-        <v>10.4</v>
+        <v>7.7</v>
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
@@ -19269,7 +19283,7 @@
       <c r="M219" s="4" t="inlineStr"/>
       <c r="N219" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 11: 120 carros ≈ 10 × 6 m</t>
+          <t>W-CAR 11 con la demanda 2035: 84 carros</t>
         </is>
       </c>
     </row>
@@ -19335,7 +19349,7 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Pulmón de pintados: 15 filas de 8 carros por modelo y lote (120)</t>
+          <t>Pulmón de pintados: 7 filas de 7 carros por modelo y lote (49)</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -19355,16 +19369,16 @@
         <v>3.45</v>
       </c>
       <c r="G221" s="5" t="n">
-        <v>60.35</v>
+        <v>59.75</v>
       </c>
       <c r="H221" s="5" t="n">
-        <v>12.75</v>
+        <v>8.35</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J221" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
@@ -19377,7 +19391,7 @@
       <c r="M221" s="4" t="inlineStr"/>
       <c r="N221" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 12: 120 carros ≈ 10 × 7 m, al lado del puesto 13</t>
+          <t>W-CAR 12 con la demanda 2035: 49 carros</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19947,7 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>Muestra: lugares 1 a 16</t>
+          <t>Muestra: lugares 1 a 6</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
@@ -19950,19 +19964,19 @@
         <v>39.85</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="G232" s="5" t="n">
-        <v>43.85</v>
+        <v>43.55</v>
       </c>
       <c r="H232" s="5" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="I232" s="5" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J232" s="5" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="K232" s="4" t="inlineStr">
         <is>
@@ -19975,7 +19989,7 @@
       <c r="M232" s="4" t="inlineStr"/>
       <c r="N232" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 14: 30 lugares de 0,5 m²</t>
+          <t>W-CAR 14 con la muestra de 2035: 17 lugares de 0,5 m²</t>
         </is>
       </c>
     </row>
@@ -19987,7 +20001,7 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Muestra: lugares 17 a 30</t>
+          <t>Muestra: lugares 7 a 17</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -20004,16 +20018,16 @@
         <v>39.85</v>
       </c>
       <c r="F233" s="5" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="G233" s="5" t="n">
-        <v>43.85</v>
+        <v>43.55</v>
       </c>
       <c r="H233" s="5" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J233" s="5" t="n">
         <v>1.4</v>
@@ -20029,7 +20043,7 @@
       <c r="M233" s="4" t="inlineStr"/>
       <c r="N233" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 14: 30 lugares de 0,5 m²</t>
+          <t>W-CAR 14 con la muestra de 2035: 17 lugares de 0,5 m²</t>
         </is>
       </c>
     </row>
@@ -20058,19 +20072,19 @@
         <v>39.75</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>6.3</v>
+        <v>5.35</v>
       </c>
       <c r="G234" s="5" t="n">
         <v>40</v>
       </c>
       <c r="H234" s="5" t="n">
-        <v>7.4</v>
+        <v>6.15</v>
       </c>
       <c r="I234" s="5" t="n">
         <v>0.25</v>
       </c>
       <c r="J234" s="5" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K234" s="4" t="inlineStr">
         <is>
@@ -20109,16 +20123,16 @@
         </is>
       </c>
       <c r="E235" s="5" t="n">
-        <v>42.4</v>
+        <v>41.5</v>
       </c>
       <c r="F235" s="5" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="G235" s="5" t="n">
-        <v>44.4</v>
+        <v>43.5</v>
       </c>
       <c r="H235" s="5" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="I235" s="5" t="n">
         <v>2</v>
@@ -20163,16 +20177,16 @@
         </is>
       </c>
       <c r="E236" s="5" t="n">
-        <v>40.8</v>
+        <v>40.1</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="G236" s="5" t="n">
-        <v>42</v>
+        <v>41.3</v>
       </c>
       <c r="H236" s="5" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="I236" s="5" t="n">
         <v>1.2</v>
@@ -20217,16 +20231,16 @@
         </is>
       </c>
       <c r="E237" s="5" t="n">
-        <v>39.9</v>
+        <v>42</v>
       </c>
       <c r="F237" s="5" t="n">
-        <v>9.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G237" s="5" t="n">
-        <v>41.4</v>
+        <v>43.5</v>
       </c>
       <c r="H237" s="5" t="n">
-        <v>10.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I237" s="5" t="n">
         <v>1.5</v>
@@ -20257,7 +20271,7 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>Liberados: 10 filas de 10 carros (100)</t>
+          <t>Liberados: 9 filas de 8 carros (70)</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
@@ -20271,22 +20285,22 @@
         </is>
       </c>
       <c r="E238" s="5" t="n">
-        <v>24.75</v>
+        <v>24.85</v>
       </c>
       <c r="F238" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="G238" s="5" t="n">
-        <v>30.65</v>
+        <v>31.15</v>
       </c>
       <c r="H238" s="5" t="n">
-        <v>12.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="J238" s="5" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="K238" s="4" t="inlineStr">
         <is>
@@ -20299,7 +20313,7 @@
       <c r="M238" s="4" t="inlineStr"/>
       <c r="N238" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16: una semana de producción, ≈ 6 × 10 m</t>
+          <t>W-CAR 16 con la demanda 2035: una semana, 70 carros</t>
         </is>
       </c>
     </row>
@@ -20311,7 +20325,7 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Retenidos: 15 filas de 12 carros (180)</t>
+          <t>Retenidos: 10 filas de 8 carros (74)</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
@@ -20325,22 +20339,22 @@
         </is>
       </c>
       <c r="E239" s="5" t="n">
-        <v>30.75</v>
+        <v>31.95</v>
       </c>
       <c r="F239" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="G239" s="5" t="n">
-        <v>39.65</v>
+        <v>38.95</v>
       </c>
       <c r="H239" s="5" t="n">
-        <v>12.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="J239" s="5" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="K239" s="4" t="inlineStr">
         <is>
@@ -20353,7 +20367,7 @@
       <c r="M239" s="4" t="inlineStr"/>
       <c r="N239" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16: hasta 180 carros, ≈ 9 × 10 m</t>
+          <t>W-CAR 16 con la demanda 2035: 1,8 semanas de matafuegos, 74 carros</t>
         </is>
       </c>
     </row>
@@ -20419,7 +20433,7 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Zona de rechazados (roja)</t>
+          <t>Zona de rechazados (roja): 23 carros</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -20433,19 +20447,19 @@
         </is>
       </c>
       <c r="E241" s="5" t="n">
-        <v>34.6</v>
+        <v>35.6</v>
       </c>
       <c r="F241" s="5" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G241" s="5" t="n">
         <v>39.6</v>
       </c>
       <c r="H241" s="5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J241" s="5" t="n">
         <v>3</v>
@@ -20461,7 +20475,7 @@
       <c r="M241" s="4" t="inlineStr"/>
       <c r="N241" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16: ≈ 5 × 3 m</t>
+          <t>W-CAR 16: el lote de 50 kg de 2035 a 0,5 m², 4 × 3 m</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20843,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cantidades del Word de carros (W-CAR, tablas de espacios de los puestos 11, 12, 14 y 16).</t>
+          <t>Reglas del Word de carros (W-CAR, puestos 11, 12, 14 y 16) aplicadas al mes pico de 2035 (X-CAR, Plan mensual): 69,8 recipientes por semana (40,8 matafuegos y 29,0 cilindros vendidos vacíos), 14,0 por día.</t>
         </is>
       </c>
     </row>
@@ -20851,12 +20865,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Criterio de W-CAR</t>
+          <t>Regla de W-CAR aplicada a 2035</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Medida de W-CAR</t>
+          <t>Medida en planta</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -20883,16 +20897,16 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 11: hasta 100 carros (una semana) más los que se hacen mientras se espera el camión</t>
+          <t>W-CAR 11: 1 semana + 1 día de espera del camión (100 + 20 en el Word). 2035: 69,8 + 14,0 (entran en 1 semirremolque)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>≈ 10 × 6 m</t>
+          <t>5,1 × 7,7 m</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -20913,16 +20927,16 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 12: el mismo tamaño que el pulmón de despacho, al lado del puesto 13</t>
+          <t>W-CAR 12: como el 11 (1 semana + 1 día), sólo lo que va al 13 (los cilindros vacíos van a liberados). 2035: 40,8 × 1,2</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>≈ 10 × 7 m</t>
+          <t>4,5 × 4,9 m</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -20943,16 +20957,16 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 14: unos 25 por semana durante 7 días, más los que esperan el puesto 17</t>
+          <t>W-CAR 14: muestra de la tabla del Word con los lotes de 2035 (3 + 8 + 1,5 + 1,5 = 14,0 por semana) × 30 / 25</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>5,0 × 5,0 m</t>
+          <t>4,0 × 4,0 m</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -20973,16 +20987,16 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16: el lote de una semana se libera al final de la siguiente: hasta unos 180 carros</t>
+          <t>W-CAR 16: el lote de la semana y casi todo el siguiente (180 = 1,8 semanas en el Word). 2035: 1,8 × 40,8 matafuegos</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>≈ 9 × 10 m</t>
+          <t>7,0 × 5,1 m</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>180</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -20998,21 +21012,21 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Lotes liberados hasta el despacho</t>
+          <t>Lotes liberados y cilindros vendidos vacíos hasta el despacho</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16: una semana de producción, unos 100 carros</t>
+          <t>W-CAR 16: una semana de producción (matafuegos y cilindros vendidos vacíos). 2035: 69,8</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>≈ 6 × 10 m</t>
+          <t>6,3 × 5,1 m</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -21033,18 +21047,16 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16: zona chica, casi nunca se usa</t>
+          <t>W-CAR 16: el lote rechazado entero; el mayor de 2035 es el de 50 kg (22,4 por semana)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>≈ 5 × 3 m</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,0 × 3,0 m</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/salida/v10/Layout_v10_zonas_y_equipos.xlsx
+++ b/salida/v10/Layout_v10_zonas_y_equipos.xlsx
@@ -15,7 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Puertas" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secciones del almacén" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portones del predio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alturas" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medios de escape" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matafuegos" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cumplimiento legal" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alturas" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,10 +608,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>179.8</v>
+        <v>302.5</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="12">
@@ -618,10 +621,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>135.4</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -631,10 +634,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1136.3</v>
+        <v>1149</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="14">
@@ -662,6 +665,2066 @@
       <c r="C15" s="4" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Matafuegos (1 cada 200 m² y a 15 m o menos de todo punto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Los del riesgo del lugar están en el modelo; el resto los ubica la cobertura de 15 m (seguridad.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MF-01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>AL-PV</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: AL-PV</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>MF-02</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: PN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>MF-03</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: PN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>MF-04</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>AL-B</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Almacén: montante del R1 hacia AL-B, con protección</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>MF-05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>AL-B</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Almacén: montante del R1 hacia AL-B, con protección</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MF-06</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: M-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>MF-07</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: M-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>MF-08</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ABC 50 kg rodante</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>M-18</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Cuelgue y cabina de pintura en polvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>MF-09</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>M-19</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: M-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MF-10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ABC 50 kg rodante</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>A2-S</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Almacén de MP: cartón y pallets del R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MF-11</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>AL-CC</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: AL-CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>MF-12</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>A2-S</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: A2-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>MF-13</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>M-PV</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: M-PV</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>MF-14</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>C-67</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: C-67</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>MF-15</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>CO₂ 5 kg</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>SV-TG</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Tablero general (clase C, no deja residuo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>MF-16</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ABC 50 kg rodante</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>SR-RE</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Recepción, cuarentena, fleje y polvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>MF-17</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>SR-PQ</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Depósito de polvo y de pintura en polvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>MF-18</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>SV-RE</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Residuos especiales</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>MF-19</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>C-17</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: C-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>MF-20</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>M-20</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: M-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>MF-21</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>M-20</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: M-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MF-22</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>SV-CP</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: SV-CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>MF-23</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>PS-4</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Aceites e inflamables (junto a la puerta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>MF-24</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>C-17P</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: C-17P</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>MF-25</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>PT-M2</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura de 15 m: PT-M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>MF-E1</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Exterior</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Jaula de gases (junto a la puerta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>MF-E2</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>ABC 10 kg</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Exterior</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Cobertizo de autoelevadores</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cumplimiento legal de seguridad e higiene</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cláusulas tomadas de copias secundarias: confirmarlas con el texto oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Requisito</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Norma</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se resuelve en el plano</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Escape</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2 unidades de ancho (1,10 m) por salida; 0,55 + 0,45 m</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 anexo VII, 3</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>9 salidas de 1,10 a 1,20 m que abren hacia afuera</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Escape</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>N = superficie / 16 m²; n = N / 100 unidades; n/4 + 1 medios</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 anexo VII, 3</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>N = 224, n = 3 -&gt; 1 medio y 1.55 m; hay 9 salidas y 10.6 m</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Escape</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Recorrido hasta una salida</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Anexo VII: 40 m (a la caja de escalera)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Máximo 38.0 m por la línea de libre trayectoria (grilla de 0,5 m)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Criterio</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Escape</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Puertas en el sentido de la evacuación, sin trabas</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 anexo VII, 3</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Abren hacia afuera, con barral antipánico; puntos de encuentro exteriores</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Señales</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Vías de evacuación con líneas amarillas y flechas</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 art. 80</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Flechas en cada pasillo y senda hacia la salida más cercana</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Señales</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Colores y señales de seguridad</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 arts. 77-78; IRAM 10005</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>SALIDA en cada salida; prohibición, advertencia y obligación por zona</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Pasillos</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Demarcados con dos franjas o piso pintado</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 art. 79</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Carriles con dos líneas, sendas en cebra, pasillos de operarios con dos líneas</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Iluminación</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Emergencia de 30 lx a 0,80 m en los medios de escape</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 art. 76</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>70 luminarias autónomas: salidas, cada 10 m de pasillo y cada local</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Verificar lux</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Iluminación</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Niveles por tarea y medición</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 anexo IV; Res. SRT 84/12</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Proyecto luminotécnico y medición con la planta en marcha</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>A completar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Incendio</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>1 matafuego cada 200 m²</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 cap. 18 y anexo VII</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>3572 m² -&gt; 18; hay 25 en la nave, 2 afuera y 2 en el anexo</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Incendio</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Recorrido al matafuego: 20 m (clase A), 15 m (clase B)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 cap. 18 y anexo VII</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Todo punto libre de la nave a 15 m o menos (se toma clase B en todo)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Incendio</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Potencial extintor y condiciones según la carga de fuego</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 anexo VII</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Falta el estudio de carga de fuego por sector</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>A completar</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Gases</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Cilindros parados, sujetos, ventilados, llenos y vacíos aparte</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 art. 142</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Jaula exterior JG, jaula de tubos CU-2 y batería C13-5 encadenada</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Autoelevad.</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Carga de baterías en lugar designado y equipado</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Res. SRT 960/15 art. 22</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Cobertizo CAE: cargador, lavaojos y matafuego; estacionamiento</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Autoelevad.</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Señalización de las zonas de circulación</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Res. SRT 960/15</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Carriles demarcados, cruces de la baranda y carteles</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Ruido</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>85 dBA en 8 h: protección auditiva y señal</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Res. MTESS 295/03; Res. SRT 85/12</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Zonas de protección auditiva de los puestos que la piden en los Word</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Medir</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ventilación</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Captación de humos y polvos en la fuente</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 cap. 11</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Extracción en soldaduras, amolado, cargas de polvo, granallado y ensayos</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>EPP</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Entrega con constancia firmada</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Res. SRT 299/11</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Pañol de EPP SV-EP con mostrador y registro</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Prim. auxilios</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Botiquín y atención inmediata</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Ley 19.587; Dec. 351/79</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sala en SV-EP (camilla, botiquín, lavaojos) y 5 botiquines en planta</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Lavaojos</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Lavado de ojos (ficha de seguridad del polvo ABC)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Criterio (W-MAN: ficha en el puesto)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>En las cargas y descargas de polvo, en SV-EP y en el cobertizo</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Criterio</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Provisión y reserva para uso humano</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 art. 57</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>4 bebederos; reserva de 50 L por persona y jornada con la dotación X-DT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>A completar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sanitarios</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Artefactos y armarios por sexo</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 art. 49</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Verificado con la dotación de X-DT (FL_PI10_05)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Residuos</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Depósito transitorio, manifiesto y gestor</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Ley 24.051; Ley 11.720 (PBA)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>SV-RE con tambores sobre batea y puerta P8 al exterior</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Inflamables</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Fuera de los puestos, en local ventilado</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 cap. 18</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>SV-IN contra el muro exterior: armario de seguridad y batea</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Máquinas</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Resguardos, paradas de emergencia, zonas delimitadas</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 351/79 cap. 15</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Los de W-MAN y W-CAR en cada puesto (zona de la envolvedora)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Accesibilidad</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Baño accesible, rampas de 8 %, cajón reservado</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Ley 24.314</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Anexo de administración (FL_PI10_05)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Gas natural</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Instalación industrial y ERM</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>NAG-201 (ENARGAS)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>ERM en la línea municipal y cañería a los hornos de la pintura</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>A completar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Higiene y Seguridad y medicina laboral</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Dec. 1338/96</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Externos (X-DT, notas M29)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Alturas usadas en los cortes (FL_PI10_06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Elemento</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Alto (m)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>M4-3</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>ET Sangiacomo T 63R: 2790 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>M3-2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Cotización Leapion: 1200 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>M8-1</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Catálogo Firesafer FS-RM01: 1250 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>M9-1</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ET Getweld ZF-500 (referencia): 1600 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>M7-1</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Catálogo Firesafer FS-HFM1: 1580 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>M10-1</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>ET Del Fabro: 1800 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>M11-1</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Presupuesto Pilman SWM-400: 1280 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>M14-*</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Catálogo Firesafer FS-JD12A: 1350 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>M15-*</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>ET secadora Yukon: 1750 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>M16-1</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Cotización Airblast G-100: 2200 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>M19-1</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ET línea Firesafer: 25 × 8 × 4 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>M20-2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Ficha Yukon M-000121: 1200 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>M23-1</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Catálogo Filling Line FS-SS100: 900 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>C17-2</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR 17: recinto de 3 m de alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>C13-3</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR 13: bastidor de 2,8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>RC-*</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR 1 tabla 5: racks de carros de ≈ 3 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>R1-*</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Criterio: la carga de arriba llega a la elevación máxima del Heli CPCD50, 6 m (W-CAR 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PTM-*</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Criterio: 5 niveles hasta la elevación máxima del Heli CPCD50, 6 m (W-CAR 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>PQ-*</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR 1: big bag de 1,2 m de alto, apilado de a 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>filas</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Hoja de especificaciones «Polvos carros»: carro de 50 kg, 1160 mm (25 kg 1085; 100 kg 1360)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>rodantes</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Hoja de especificaciones «Polvos carros»: carro de 50 kg, 1160 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>lugar</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Hoja de especificaciones «Polvos carros»: carro de 50 kg, 1160 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>banco</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR 1: mesa de trabajo metálica de unos 86 cm de alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>mesa_control</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR 1: mesa de 86 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>inspeccion</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR 1: mesa de 86 cm</t>
         </is>
       </c>
     </row>
@@ -676,7 +2739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2615,22 +4678,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>LB-1</t>
+          <t>SV-RE</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Libre (reserva)</t>
+          <t>Depósito transitorio de residuos especiales (retira un gestor habilitado, con manifiesto)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Libre / reserva</t>
+          <t>Servicios técnicos (mantenimiento, calidad, aire, energía)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -2661,7 +4724,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Croquis del usuario: espacio libre</t>
+          <t>W-CAR 17: el polvo que no pasa los controles «se entrega a un gestor de residuos con su manifiesto»; Ley 24.051 y Ley 11.720 (PBA): depósito transitorio de residuos especiales; puerta P8 al exterior para el retiro</t>
         </is>
       </c>
     </row>
@@ -5464,22 +7527,22 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>RV-S</t>
+          <t>SV-IN</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Libre (reserva de ampliación del PT y de los ensayos)</t>
+          <t>Depósito de aceites e inflamables (armario de seguridad y tambores sobre batea)</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Libre / reserva</t>
+          <t>Servicios técnicos (mantenimiento, calidad, aire, energía)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
@@ -5489,19 +7552,19 @@
         <v>0</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>38.25</v>
+        <v>28.4</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>7.95</v>
+        <v>3.6</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>13.55</v>
+        <v>3.7</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>7.95</v>
+        <v>3.6</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>107.72</v>
+        <v>13.32</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -5510,24 +7573,24 @@
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>Lo que queda de la nave de 76 m con la demanda 2035 (la nave podría acortarse un vano de 7,6 m)</t>
+          <t>Dec. 351/79 (prevención de incendios): los inflamables fuera de los puestos, en local propio contra el muro exterior y ventilado; contenido: aceites de mantenimiento, grasa de silicona (W-MAN 21) y alcohol del etiquetado (W-CAR 15)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>C-17P</t>
+          <t>SV-RR</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>17 Paso de la muestra al patio de ensayos (P5)</t>
+          <t>Residuos reciclables y asimilables (cartón, film, zunchos y madera)</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Carros 25 a 100 kg</t>
+          <t>Servicios técnicos (mantenimiento, calidad, aire, energía)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -5536,25 +7599,25 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="F96" s="4" t="n">
-        <v>0</v>
+        <v>24.7</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>3.6</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>40.25</v>
+        <v>28.4</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>7.95</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>7.95</v>
+        <v>4.35</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>15.9</v>
+        <v>16.09</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -5563,204 +7626,210 @@
       </c>
       <c r="M96" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 17: la rodadura (1 km, caída de 20 cm y choque) se hace afuera</t>
+          <t>W-MAN 25 y W-CAR 11 y 16: cajas, cartones separadores, film y pallets rotos; contenedores separados por tipo</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>C-15</t>
+          <t>PS-4</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>15 Etiquetado e inspección final</t>
+          <t>Paso peatonal a la salida de emergencia PE-4</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Carros 25 a 100 kg</t>
+          <t>Pasillos y sendas</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>pasillo</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>40.25</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>3.95</v>
+        <v>28.4</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>44.25</v>
+        <v>30</v>
       </c>
       <c r="H97" s="5" t="n">
         <v>7.95</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>4</v>
+        <v>7.95</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v>9</v>
+        <v>12.72</v>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 15: ≈ 3,5 × 2,5 m</t>
+          <t>1,6 m: une la banda de los ensayos con PE-4 (Dec. 351/79, anexo VII: medios de escape)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>C-16X</t>
+          <t>SV-LI</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>16 Rechazados (rojo) y revisión al 100 %</t>
+          <t>Cuarto de limpieza (fregadora, aspiradoras industriales y carros)</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Depósitos de producto terminado</t>
+          <t>Servicios técnicos (mantenimiento, calidad, aire, energía)</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>40.25</v>
+        <v>30</v>
       </c>
       <c r="F98" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>44.25</v>
+        <v>38.25</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>4</v>
+        <v>8.25</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>6</v>
+        <v>29.7</v>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M98" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16: rechazados, 12 carros a 0,5 m²</t>
+          <t>W-MAN, carga de polvo: «limpieza frecuente, porque el polvo en el piso resbala»; W-CAR 17: el recinto se limpia con aspiradora; Dec. 351/79 (orden y limpieza de los lugares de trabajo)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>C-16</t>
+          <t>SV-EP</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>16 Depósito de PT de carros: retenidos (amarillo), liberados (verde) y despacho por P2</t>
+          <t>Pañol de EPP y sala de primeros auxilios</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Depósitos de producto terminado</t>
+          <t>Servicios técnicos (mantenimiento, calidad, aire, energía)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>44.25</v>
-      </c>
-      <c r="F99" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>3.6</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>57.75</v>
+        <v>38.25</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>7.95</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>13.5</v>
+        <v>8.25</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>7.95</v>
+        <v>4.35</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>107.33</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>66</v>
+        <v>35.89</v>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>W-CAR, tabla de espacios del puesto 16: 0,5 m² por carro y los pasillos; 62 retenidos y 70 liberados (demanda 2035)</t>
+          <t>Res. SRT 299/11: EPP con constancia de entrega; EPP de cada puesto según W-MAN y W-CAR; primeros auxilios: camilla, botiquín, lavamanos y lavaojos</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>PT-MA</t>
+          <t>C-17P</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Depósito de PT unificado: pasillo del autoelevador (del pasillo principal a los racks)</t>
+          <t>17 Paso de la muestra al patio de ensayos (P5)</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Pasillos y sendas</t>
+          <t>Carros 25 a 100 kg</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>pasillo</t>
+          <t>area</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>57.75</v>
+        <v>38.25</v>
       </c>
       <c r="F100" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>60.75</v>
+        <v>40.25</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>13.5</v>
+        <v>7.95</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>13.5</v>
+        <v>7.95</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>40.5</v>
+        <v>15.9</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -5769,24 +7838,24 @@
       </c>
       <c r="M100" s="4" t="inlineStr">
         <is>
-          <t>Tránsito de un solo sentido: autoelevador de 1,17 a 1,51 m de ancho + 0,75 m por lado = 3,0 m (criterio)</t>
+          <t>W-CAR 17: la rodadura (1 km, caída de 20 cm y choque) se hace afuera</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>PT-M</t>
+          <t>C-15</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Depósito de PT unificado: rack de manuales contra el muro sur</t>
+          <t>15 Etiquetado e inspección final</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Depósitos de producto terminado</t>
+          <t>Carros 25 a 100 kg</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -5795,138 +7864,344 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="F101" s="4" t="n">
-        <v>0</v>
+        <v>40.25</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>3.95</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>76</v>
+        <v>44.25</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>1.35</v>
+        <v>7.95</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>15.25</v>
+        <v>4</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>20.59</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 25: rack de PT y de cilindros en el mismo almacén, el autoelevador ubica el pallet en altura o lo carga directo al camión (P4); 70 pallets (semana 40 + diciembre 30) + 17 de revendidos (X-ALM) en 90 posiciones</t>
+          <t>W-CAR, tabla de espacios del puesto 15: ≈ 3,5 × 2,5 m</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>PT-MA2</t>
+          <t>C-16X</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Depósito de PT unificado: pasillo de los racks (a P4)</t>
+          <t>16 Rechazados (rojo) y revisión al 100 %</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Pasillos y sendas</t>
+          <t>Depósitos de producto terminado</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>pasillo</t>
+          <t>area</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>1.35</v>
+        <v>40.25</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>76</v>
+        <v>44.25</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>4.95</v>
+        <v>3.95</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>15.25</v>
+        <v>4</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15.8</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>Heli CPD15 eléctrico de 1,5 t (agregado por el pasillo angosto): apilado a 90° en 3.315 a 3.515 mm según el pallet (ficha Heli CPD15-20) -&gt; 3,6 m. El Heli CPCD50 necesitaría 4,96 m</t>
+          <t>W-CAR 16: rechazados, 12 carros a 0,5 m²</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
+          <t>C-16</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>16 Depósito de PT de carros: retenidos (amarillo), liberados (verde) y despacho por P2</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Depósitos de producto terminado</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>107.33</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="M103" s="4" t="inlineStr">
+        <is>
+          <t>W-CAR, tabla de espacios del puesto 16: 0,5 m² por carro y los pasillos; 62 retenidos y 70 liberados (demanda 2035)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>PT-MA</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Depósito de PT unificado: pasillo del autoelevador (del pasillo principal a los racks)</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Pasillos y sendas</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>pasillo</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M104" s="4" t="inlineStr">
+        <is>
+          <t>Tránsito de un solo sentido: autoelevador de 1,17 a 1,51 m de ancho + 0,75 m por lado = 3,0 m (criterio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>PT-M</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Depósito de PT unificado: rack de manuales contra el muro sur</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Depósitos de producto terminado</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="4" t="inlineStr">
+        <is>
+          <t>W-MAN 25: rack de PT y de cilindros en el mismo almacén, el autoelevador ubica el pallet en altura o lo carga directo al camión (P4); 70 pallets (semana 40 + diciembre 30) + 17 de revendidos (X-ALM) en 90 posiciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>PT-MA2</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Depósito de PT unificado: pasillo de los racks (a P4)</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Pasillos y sendas</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>pasillo</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M106" s="4" t="inlineStr">
+        <is>
+          <t>Heli CPD15 eléctrico de 1,5 t (agregado por el pasillo angosto): apilado a 90° en 3.315 a 3.515 mm según el pallet (ficha Heli CPD15-20) -&gt; 3,6 m. El Heli CPCD50 necesitaría 4,96 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
           <t>PT-M2</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>Depósito de PT unificado: rack de manuales y entrega de la envolvedora</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>Depósitos de producto terminado</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D107" s="4" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="E103" s="5" t="n">
+      <c r="E107" s="5" t="n">
         <v>60.75</v>
       </c>
-      <c r="F103" s="5" t="n">
+      <c r="F107" s="5" t="n">
         <v>4.95</v>
       </c>
-      <c r="G103" s="5" t="n">
+      <c r="G107" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="H103" s="5" t="n">
+      <c r="H107" s="5" t="n">
         <v>6.15</v>
       </c>
-      <c r="I103" s="5" t="n">
+      <c r="I107" s="5" t="n">
         <v>15.25</v>
       </c>
-      <c r="J103" s="5" t="n">
+      <c r="J107" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="K103" s="5" t="n">
+      <c r="K107" s="5" t="n">
         <v>18.3</v>
       </c>
-      <c r="L103" s="4" t="inlineStr">
+      <c r="L107" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M103" s="4" t="inlineStr">
+      <c r="M107" s="4" t="inlineStr">
         <is>
           <t>W-MAN 25: rack de PT y de cilindros en el mismo almacén, el autoelevador ubica el pallet en altura o lo carga directo al camión (P4); 70 pallets (semana 40 + diciembre 30) + 17 de revendidos (X-ALM) en 90 posiciones</t>
         </is>
@@ -7159,7 +9434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N298"/>
+  <dimension ref="A1:N304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20267,178 +22542,174 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>C13-1</t>
+          <t>RR-1</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Estación A: lugar del carro (cinta y control del interior)</t>
+          <t>Contenedor de 1.000 L: cartón y cajas</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>C-13</t>
+          <t>SV-RR</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>lugar</t>
+          <t>contenedores</t>
         </is>
       </c>
       <c r="E243" s="5" t="n">
-        <v>53.9</v>
+        <v>24.8</v>
       </c>
       <c r="F243" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="G243" s="5" t="n">
-        <v>56.3</v>
+        <v>26.27</v>
       </c>
       <c r="H243" s="5" t="n">
-        <v>11.5</v>
+        <v>5.17</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="J243" s="5" t="n">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="K243" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L243" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M243" s="4" t="inlineStr"/>
       <c r="N243" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 13: 2,4 × 2,2 m, del lado del pulmón de pintados</t>
+          <t>W-MAN 25 y W-CAR 16 (materiales de embalaje); contenedor de 1.000 L como el de scrap (W-CAR 2)</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>C13-2</t>
+          <t>RR-2</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Estación B: balanza de 300 kg con rampa y cargadora por vacío Yukon M-000121</t>
+          <t>Contenedor de 1.000 L: film y zunchos</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>C-13</t>
+          <t>SV-RR</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>carga_polvo</t>
+          <t>contenedores</t>
         </is>
       </c>
       <c r="E244" s="5" t="n">
-        <v>49.9</v>
+        <v>24.8</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="G244" s="5" t="n">
-        <v>52.9</v>
+        <v>26.27</v>
       </c>
       <c r="H244" s="5" t="n">
-        <v>11.6</v>
+        <v>6.72</v>
       </c>
       <c r="I244" s="5" t="n">
-        <v>3</v>
+        <v>1.47</v>
       </c>
       <c r="J244" s="5" t="n">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="K244" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L244" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M244" s="4" t="inlineStr"/>
       <c r="N244" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 13: 3,0 × 2,6 m</t>
+          <t>W-MAN 25 y W-CAR 16 (materiales de embalaje); contenedor de 1.000 L como el de scrap (W-CAR 2)</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>C13-3</t>
+          <t>RR-3</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Bastidor de descarga del big bag con tolva (alto 2,8 m)</t>
+          <t>Pallets rotos y madera (pila en el piso)</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>C-13</t>
+          <t>SV-RR</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>bastidor</t>
+          <t>pallets_q</t>
         </is>
       </c>
       <c r="E245" s="5" t="n">
-        <v>50.6</v>
+        <v>26.6</v>
       </c>
       <c r="F245" s="5" t="n">
-        <v>12.2</v>
+        <v>3.75</v>
       </c>
       <c r="G245" s="5" t="n">
-        <v>52.2</v>
+        <v>27.8</v>
       </c>
       <c r="H245" s="5" t="n">
-        <v>13.4</v>
+        <v>4.75</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J245" s="5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K245" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L245" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M245" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="M245" s="4" t="inlineStr"/>
       <c r="N245" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 13: 1,6 × 1,2 m, con acceso para el autoelevador</t>
+          <t>X-ALM: pallet de madera 1200 × 1000; los rotos salen con los reciclables</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>C13-4</t>
+          <t>C13-1</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Estación C: lugar del carro (manga, traba, precinto y tarjeta)</t>
+          <t>Estación A: lugar del carro (cinta y control del interior)</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
@@ -20452,19 +22723,19 @@
         </is>
       </c>
       <c r="E246" s="5" t="n">
-        <v>45.3</v>
+        <v>53.9</v>
       </c>
       <c r="F246" s="5" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="G246" s="5" t="n">
-        <v>47.6</v>
+        <v>56.3</v>
       </c>
       <c r="H246" s="5" t="n">
         <v>11.5</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J246" s="5" t="n">
         <v>2.2</v>
@@ -20480,19 +22751,19 @@
       <c r="M246" s="4" t="inlineStr"/>
       <c r="N246" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 13: 2,3 × 2,2 m, del lado del etiquetado</t>
+          <t>W-CAR 13: 2,4 × 2,2 m, del lado del pulmón de pintados</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>C13-5</t>
+          <t>C13-2</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Batería de nitrógeno (11 tubos de 50 L) en jaula, con manifold</t>
+          <t>Estación B: balanza de 300 kg con rampa y cargadora por vacío Yukon M-000121</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -20502,51 +22773,51 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>bateria_gas</t>
+          <t>carga_polvo</t>
         </is>
       </c>
       <c r="E247" s="5" t="n">
-        <v>44.4</v>
+        <v>49.9</v>
       </c>
       <c r="F247" s="5" t="n">
-        <v>12.55</v>
+        <v>9</v>
       </c>
       <c r="G247" s="5" t="n">
-        <v>47</v>
+        <v>52.9</v>
       </c>
       <c r="H247" s="5" t="n">
-        <v>13.45</v>
+        <v>11.6</v>
       </c>
       <c r="I247" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J247" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="J247" s="5" t="n">
-        <v>0.9</v>
-      </c>
       <c r="K247" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L247" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M247" s="4" t="inlineStr"/>
       <c r="N247" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 13: 2,6 × 0,9 m</t>
+          <t>W-CAR 13: 3,0 × 2,6 m</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>C13-6</t>
+          <t>C13-3</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Colector de polvo de 3 HP (aspiración localizada en la boca)</t>
+          <t>Bastidor de descarga del big bag con tolva (alto 2,8 m)</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
@@ -20556,26 +22827,26 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>colector10</t>
+          <t>bastidor</t>
         </is>
       </c>
       <c r="E248" s="5" t="n">
-        <v>52.5</v>
+        <v>50.6</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="G248" s="5" t="n">
-        <v>53.3</v>
+        <v>52.2</v>
       </c>
       <c r="H248" s="5" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J248" s="5" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="K248" s="4" t="inlineStr">
         <is>
@@ -20585,22 +22856,26 @@
       <c r="L248" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M248" s="4" t="inlineStr"/>
+      <c r="M248" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="N248" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 13: equipos y herramientas</t>
+          <t>W-CAR 13: 1,6 × 1,2 m, con acceso para el autoelevador</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>C13-7</t>
+          <t>C13-4</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Estanterías de válvulas, mangas, ruedas y ejes, con cajones (1 y 2)</t>
+          <t>Estación C: lugar del carro (manga, traba, precinto y tarjeta)</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
@@ -20610,51 +22885,51 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>estanteria</t>
+          <t>lugar</t>
         </is>
       </c>
       <c r="E249" s="5" t="n">
-        <v>47.2</v>
+        <v>45.3</v>
       </c>
       <c r="F249" s="5" t="n">
-        <v>12.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G249" s="5" t="n">
-        <v>50.2</v>
+        <v>47.6</v>
       </c>
       <c r="H249" s="5" t="n">
-        <v>13.45</v>
+        <v>11.5</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J249" s="5" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="K249" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L249" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M249" s="4" t="inlineStr"/>
       <c r="N249" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 13: 3 × (2,0 × 0,5 m)</t>
+          <t>W-CAR 13: 2,3 × 2,2 m, del lado del etiquetado</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>C13-8</t>
+          <t>C13-5</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Estantería de válvulas, mangas, ruedas y ejes, con cajones (3)</t>
+          <t>Batería de nitrógeno en uso (11 tubos de 50 L a 200 bar, alquilada) en jaula, encadenada, con manifold y regulador a 14 bar</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
@@ -20664,30 +22939,30 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>estanteria</t>
+          <t>bateria_gas</t>
         </is>
       </c>
       <c r="E250" s="5" t="n">
-        <v>53.4</v>
+        <v>44.3</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>12.95</v>
+        <v>9.6</v>
       </c>
       <c r="G250" s="5" t="n">
-        <v>56.4</v>
+        <v>45.2</v>
       </c>
       <c r="H250" s="5" t="n">
-        <v>13.45</v>
+        <v>12.2</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J250" s="5" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="K250" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L250" s="4" t="n">
@@ -20696,48 +22971,48 @@
       <c r="M250" s="4" t="inlineStr"/>
       <c r="N250" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 13: 3 × (2,0 × 0,5 m)</t>
+          <t>W-CAR 13: «batería de nitrógeno en jaula, con manifold, 2,6 × 0,9 m, contra la pared, encadenada» (contra el muro de la sala de pérdidas, fuera del carril del autoelevador)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>C14-1</t>
+          <t>LO-2</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Muestra: lugares 1 a 6</t>
+          <t>Lavaojos de emergencia de la carga de polvo de carros</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>C-14</t>
+          <t>C-13</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>rodantes</t>
+          <t>lavaojos</t>
         </is>
       </c>
       <c r="E251" s="5" t="n">
-        <v>40.4</v>
+        <v>48.2</v>
       </c>
       <c r="F251" s="5" t="n">
-        <v>12.7</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G251" s="5" t="n">
-        <v>44.1</v>
+        <v>48.8</v>
       </c>
       <c r="H251" s="5" t="n">
-        <v>13.4</v>
+        <v>8.65</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J251" s="5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K251" s="4" t="inlineStr">
         <is>
@@ -20750,52 +23025,52 @@
       <c r="M251" s="4" t="inlineStr"/>
       <c r="N251" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 14 con la muestra de 2035: 18 lugares de 0,5 m²</t>
+          <t>Criterio: la ficha de seguridad del polvo ABC (W-MAN, carga de polvo: «ficha de seguridad del polvo en el puesto») indica lavar los ojos con abundante agua</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>C14-2</t>
+          <t>C13-6</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Muestra: lugares 7 a 18</t>
+          <t>Colector de polvo de 3 HP (aspiración localizada en la boca)</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>C-14</t>
+          <t>C-13</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>rodantes</t>
+          <t>colector10</t>
         </is>
       </c>
       <c r="E252" s="5" t="n">
-        <v>40.4</v>
+        <v>52.5</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="G252" s="5" t="n">
-        <v>44.1</v>
+        <v>53.3</v>
       </c>
       <c r="H252" s="5" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="I252" s="5" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J252" s="5" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="K252" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L252" s="4" t="n">
@@ -20804,52 +23079,52 @@
       <c r="M252" s="4" t="inlineStr"/>
       <c r="N252" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 14 con la muestra de 2035: 18 lugares de 0,5 m²</t>
+          <t>W-CAR 13: equipos y herramientas</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>C14-3</t>
+          <t>C13-7</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Split frío/calor BGH 3000F y registrador</t>
+          <t>Estanterías de válvulas, mangas, ruedas y ejes, con cajones (1 y 2)</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>C-14</t>
+          <t>C-13</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>split</t>
+          <t>estanteria</t>
         </is>
       </c>
       <c r="E253" s="5" t="n">
-        <v>40.3</v>
+        <v>47.2</v>
       </c>
       <c r="F253" s="5" t="n">
-        <v>11.85</v>
+        <v>12.95</v>
       </c>
       <c r="G253" s="5" t="n">
-        <v>40.55</v>
+        <v>50.2</v>
       </c>
       <c r="H253" s="5" t="n">
-        <v>12.65</v>
+        <v>13.45</v>
       </c>
       <c r="I253" s="5" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J253" s="5" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K253" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L253" s="4" t="n">
@@ -20858,48 +23133,48 @@
       <c r="M253" s="4" t="inlineStr"/>
       <c r="N253" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 14: en la pared</t>
+          <t>W-CAR 13: 3 × (2,0 × 0,5 m)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>C15-1</t>
+          <t>C13-8</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Lugares de los 2 carros que se etiquetan</t>
+          <t>Estantería de válvulas, mangas, ruedas y ejes, con cajones (3)</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>C-15</t>
+          <t>C-13</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>lugar</t>
+          <t>estanteria</t>
         </is>
       </c>
       <c r="E254" s="5" t="n">
-        <v>42</v>
+        <v>53.4</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>6</v>
+        <v>12.95</v>
       </c>
       <c r="G254" s="5" t="n">
-        <v>44</v>
+        <v>56.4</v>
       </c>
       <c r="H254" s="5" t="n">
-        <v>6.8</v>
+        <v>13.45</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J254" s="5" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K254" s="4" t="inlineStr">
         <is>
@@ -20907,57 +23182,57 @@
         </is>
       </c>
       <c r="L254" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M254" s="4" t="inlineStr"/>
       <c r="N254" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 15: 2 × (1,0 × 0,8 m)</t>
+          <t>W-CAR 13: 3 × (2,0 × 0,5 m)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>C15-2</t>
+          <t>C14-1</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Mesa con calcomanías, plantillas y alcohol</t>
+          <t>Muestra: lugares 1 a 6</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>C-15</t>
+          <t>C-14</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>etiquetadora</t>
+          <t>rodantes</t>
         </is>
       </c>
       <c r="E255" s="5" t="n">
-        <v>40.45</v>
+        <v>40.4</v>
       </c>
       <c r="F255" s="5" t="n">
-        <v>7.15</v>
+        <v>12.7</v>
       </c>
       <c r="G255" s="5" t="n">
-        <v>41.65</v>
+        <v>44.1</v>
       </c>
       <c r="H255" s="5" t="n">
-        <v>7.75</v>
+        <v>13.4</v>
       </c>
       <c r="I255" s="5" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J255" s="5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K255" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L255" s="4" t="n">
@@ -20966,52 +23241,52 @@
       <c r="M255" s="4" t="inlineStr"/>
       <c r="N255" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 15: 1,2 × 0,6 m</t>
+          <t>W-CAR 14 con la muestra de 2035: 18 lugares de 0,5 m²</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>C15-3</t>
+          <t>C14-2</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Zona de no conforme (roja)</t>
+          <t>Muestra: lugares 7 a 18</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>C-15</t>
+          <t>C-14</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>rodantes</t>
         </is>
       </c>
       <c r="E256" s="5" t="n">
-        <v>40.45</v>
+        <v>40.4</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>4.15</v>
+        <v>10.4</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>41.95</v>
+        <v>44.1</v>
       </c>
       <c r="H256" s="5" t="n">
-        <v>5.15</v>
+        <v>11.8</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J256" s="5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="K256" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L256" s="4" t="n">
@@ -21020,48 +23295,48 @@
       <c r="M256" s="4" t="inlineStr"/>
       <c r="N256" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 15: 1,5 × 1,0 m</t>
+          <t>W-CAR 14 con la muestra de 2035: 18 lugares de 0,5 m²</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>C16-R</t>
+          <t>C14-3</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Retenidos: 8 filas de 8 carros (62)</t>
+          <t>Split frío/calor BGH 3000F y registrador</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>C-16</t>
+          <t>C-14</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>filas</t>
+          <t>split</t>
         </is>
       </c>
       <c r="E257" s="5" t="n">
-        <v>44.35</v>
+        <v>40.3</v>
       </c>
       <c r="F257" s="5" t="n">
-        <v>1.7</v>
+        <v>11.85</v>
       </c>
       <c r="G257" s="5" t="n">
-        <v>49.95</v>
+        <v>40.55</v>
       </c>
       <c r="H257" s="5" t="n">
-        <v>6.8</v>
+        <v>12.65</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>5.6</v>
+        <v>0.25</v>
       </c>
       <c r="J257" s="5" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="K257" s="4" t="inlineStr">
         <is>
@@ -21074,106 +23349,106 @@
       <c r="M257" s="4" t="inlineStr"/>
       <c r="N257" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16 con lotes de media semana: 62 carros</t>
+          <t>W-CAR 14: en la pared</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>C16-L</t>
+          <t>C15-1</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Liberados: 9 filas de 8 carros (70)</t>
+          <t>Lugares de los 2 carros que se etiquetan</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>C-16</t>
+          <t>C-15</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>filas</t>
+          <t>lugar</t>
         </is>
       </c>
       <c r="E258" s="5" t="n">
-        <v>50.05</v>
+        <v>42</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="G258" s="5" t="n">
-        <v>56.35</v>
+        <v>44</v>
       </c>
       <c r="H258" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="I258" s="5" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J258" s="5" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="K258" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L258" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M258" s="4" t="inlineStr"/>
       <c r="N258" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16 con la demanda 2035: una semana, 70 carros</t>
+          <t>W-CAR 15: 2 × (1,0 × 0,8 m)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>C16-X</t>
+          <t>C15-2</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Zona de rechazados (roja): 12 carros</t>
+          <t>Mesa con calcomanías, plantillas y alcohol</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>C-16X</t>
+          <t>C-15</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>etiquetadora</t>
         </is>
       </c>
       <c r="E259" s="5" t="n">
-        <v>40.35</v>
+        <v>40.45</v>
       </c>
       <c r="F259" s="5" t="n">
-        <v>0.25</v>
+        <v>7.15</v>
       </c>
       <c r="G259" s="5" t="n">
-        <v>43.35</v>
+        <v>41.65</v>
       </c>
       <c r="H259" s="5" t="n">
-        <v>2.65</v>
+        <v>7.75</v>
       </c>
       <c r="I259" s="5" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J259" s="5" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="K259" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L259" s="4" t="n">
@@ -21182,52 +23457,52 @@
       <c r="M259" s="4" t="inlineStr"/>
       <c r="N259" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16: el lote de media semana de 50 kg de 2035 a 0,5 m²</t>
+          <t>W-CAR 15: 1,2 × 0,6 m</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>C16-1</t>
+          <t>C15-3</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Tarjetas de RETENIDO, LIBERADO y RECHAZADO, carteles de lote, fajas, film y bolsas (estante)</t>
+          <t>Zona de no conforme (roja)</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>C-16</t>
+          <t>C-15</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>estanteria</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="E260" s="5" t="n">
-        <v>56.45</v>
+        <v>40.45</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>5.2</v>
+        <v>4.15</v>
       </c>
       <c r="G260" s="5" t="n">
-        <v>56.95</v>
+        <v>41.95</v>
       </c>
       <c r="H260" s="5" t="n">
-        <v>6.8</v>
+        <v>5.15</v>
       </c>
       <c r="I260" s="5" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J260" s="5" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="K260" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L260" s="4" t="n">
@@ -21236,48 +23511,48 @@
       <c r="M260" s="4" t="inlineStr"/>
       <c r="N260" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 16: equipos y herramientas</t>
+          <t>W-CAR 15: 1,5 × 1,0 m</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>C17-1</t>
+          <t>C16-R</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Colector de polvo con filtro de mangas (fondo del recinto)</t>
+          <t>Retenidos: 8 filas de 8 carros (62)</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>C-17</t>
+          <t>C-16</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>colector10</t>
+          <t>filas</t>
         </is>
       </c>
       <c r="E261" s="5" t="n">
-        <v>24.9</v>
+        <v>44.35</v>
       </c>
       <c r="F261" s="5" t="n">
-        <v>10.2</v>
+        <v>1.7</v>
       </c>
       <c r="G261" s="5" t="n">
-        <v>25.9</v>
+        <v>49.95</v>
       </c>
       <c r="H261" s="5" t="n">
-        <v>11.2</v>
+        <v>6.8</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J261" s="5" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="K261" s="4" t="inlineStr">
         <is>
@@ -21290,52 +23565,52 @@
       <c r="M261" s="4" t="inlineStr"/>
       <c r="N261" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 17: ≈ 1,0 × 1,0 m</t>
+          <t>W-CAR 16 con lotes de media semana: 62 carros</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>C17-2</t>
+          <t>C16-L</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Recinto de descarga cerrado (alto 3 m), piso marcado cada 0,5 m y ventana</t>
+          <t>Liberados: 9 filas de 8 carros (70)</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>C-17</t>
+          <t>C-16</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>recinto</t>
+          <t>filas</t>
         </is>
       </c>
       <c r="E262" s="5" t="n">
-        <v>25.9</v>
+        <v>50.05</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="G262" s="5" t="n">
-        <v>36.9</v>
+        <v>56.35</v>
       </c>
       <c r="H262" s="5" t="n">
-        <v>12.2</v>
+        <v>6.8</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>11</v>
+        <v>6.3</v>
       </c>
       <c r="J262" s="5" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="K262" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L262" s="4" t="n">
@@ -21344,48 +23619,48 @@
       <c r="M262" s="4" t="inlineStr"/>
       <c r="N262" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 17: 12 × 3 m con el colector</t>
+          <t>W-CAR 16 con la demanda 2035: una semana, 70 carros</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>C17-3</t>
+          <t>C16-X</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Balanza de plataforma con rampa (en la puerta del recinto)</t>
+          <t>Zona de rechazados (roja): 12 carros</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>C-17</t>
+          <t>C-16X</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>balanza</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="E263" s="5" t="n">
-        <v>37.3</v>
+        <v>40.35</v>
       </c>
       <c r="F263" s="5" t="n">
-        <v>9.4</v>
+        <v>0.25</v>
       </c>
       <c r="G263" s="5" t="n">
-        <v>38.5</v>
+        <v>43.35</v>
       </c>
       <c r="H263" s="5" t="n">
-        <v>10.6</v>
+        <v>2.65</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J263" s="5" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="K263" s="4" t="inlineStr">
         <is>
@@ -21398,106 +23673,106 @@
       <c r="M263" s="4" t="inlineStr"/>
       <c r="N263" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 17: 1,2 × 1,2 m, del lado de la sala de pérdidas</t>
+          <t>W-CAR 16: el lote de media semana de 50 kg de 2035 a 0,5 m²</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>C17-4</t>
+          <t>C16-1</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Mesa de medición, perchero de mangas y planillas</t>
+          <t>Tarjetas de RETENIDO, LIBERADO y RECHAZADO, carteles de lote, fajas, film y bolsas (estante)</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>C-17</t>
+          <t>C-16</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>banco</t>
+          <t>estanteria</t>
         </is>
       </c>
       <c r="E264" s="5" t="n">
-        <v>38</v>
+        <v>56.45</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>12.4</v>
+        <v>5.2</v>
       </c>
       <c r="G264" s="5" t="n">
-        <v>40</v>
+        <v>56.95</v>
       </c>
       <c r="H264" s="5" t="n">
-        <v>13.2</v>
+        <v>6.8</v>
       </c>
       <c r="I264" s="5" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J264" s="5" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="K264" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L264" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M264" s="4" t="inlineStr"/>
       <c r="N264" s="4" t="inlineStr">
         <is>
-          <t>W-CAR 17: 2,0 × 0,8 m, al lado de la sala de pérdidas</t>
+          <t>W-CAR 16: equipos y herramientas</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>PU-TP</t>
+          <t>C17-1</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Terminados pintados -&gt; carga</t>
+          <t>Colector de polvo con filtro de mangas (fondo del recinto)</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>M-20</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>fchp</t>
+          <t>colector10</t>
         </is>
       </c>
       <c r="E265" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>24.9</v>
       </c>
       <c r="F265" s="5" t="n">
-        <v>12.8</v>
+        <v>10.2</v>
       </c>
       <c r="G265" s="5" t="n">
-        <v>67.38</v>
+        <v>25.9</v>
       </c>
       <c r="H265" s="5" t="n">
-        <v>13.41</v>
+        <v>11.2</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="J265" s="5" t="n">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="K265" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L265" s="4" t="n">
@@ -21506,52 +23781,52 @@
       <c r="M265" s="4" t="inlineStr"/>
       <c r="N265" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 19</t>
+          <t>W-CAR 17: ≈ 1,0 × 1,0 m</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>PU-T2.1</t>
+          <t>C17-2</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Pulmón del 2.º turno: terminados pintados esperando la carga</t>
+          <t>Recinto de descarga cerrado (alto 3 m), piso marcado cada 0,5 m y ventana</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>M-20</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>fchp</t>
+          <t>recinto</t>
         </is>
       </c>
       <c r="E266" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>25.9</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G266" s="5" t="n">
-        <v>67.38</v>
+        <v>36.9</v>
       </c>
       <c r="H266" s="5" t="n">
-        <v>11.21</v>
+        <v>12.2</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>1.28</v>
+        <v>11</v>
       </c>
       <c r="J266" s="5" t="n">
-        <v>0.61</v>
+        <v>3</v>
       </c>
       <c r="K266" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L266" s="4" t="n">
@@ -21560,52 +23835,52 @@
       <c r="M266" s="4" t="inlineStr"/>
       <c r="N266" s="4" t="inlineStr">
         <is>
-          <t>X-MAN 2035 (pintura 2 turnos, carga 1) y W-MAN (capacidad de los carros)</t>
+          <t>W-CAR 17: 12 × 3 m con el colector</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>PU-T2.2</t>
+          <t>C17-3</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Pulmón del 2.º turno: terminados pintados esperando la carga</t>
+          <t>Balanza de plataforma con rampa (en la puerta del recinto)</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>M-20</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>fchp</t>
+          <t>balanza</t>
         </is>
       </c>
       <c r="E267" s="5" t="n">
-        <v>67.47999999999999</v>
+        <v>37.3</v>
       </c>
       <c r="F267" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G267" s="5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H267" s="5" t="n">
         <v>10.6</v>
       </c>
-      <c r="G267" s="5" t="n">
-        <v>68.75999999999999</v>
-      </c>
-      <c r="H267" s="5" t="n">
-        <v>11.21</v>
-      </c>
       <c r="I267" s="5" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="J267" s="5" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="K267" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L267" s="4" t="n">
@@ -21614,52 +23889,52 @@
       <c r="M267" s="4" t="inlineStr"/>
       <c r="N267" s="4" t="inlineStr">
         <is>
-          <t>X-MAN 2035 (pintura 2 turnos, carga 1) y W-MAN (capacidad de los carros)</t>
+          <t>W-CAR 17: 1,2 × 1,2 m, del lado de la sala de pérdidas</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>PU-V2T.1</t>
+          <t>LO-3</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Pulmón del 2.º turno: cilindros vacíos esperando el embalaje</t>
+          <t>Lavaojos de emergencia de la descarga de los ensayos</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>M-20</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>fchp</t>
+          <t>lavaojos</t>
         </is>
       </c>
       <c r="E268" s="5" t="n">
-        <v>62.6</v>
+        <v>24.8</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="G268" s="5" t="n">
-        <v>63.88</v>
+        <v>25.4</v>
       </c>
       <c r="H268" s="5" t="n">
-        <v>12.11</v>
+        <v>13</v>
       </c>
       <c r="I268" s="5" t="n">
-        <v>1.28</v>
+        <v>0.6</v>
       </c>
       <c r="J268" s="5" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="K268" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L268" s="4" t="n">
@@ -21668,48 +23943,48 @@
       <c r="M268" s="4" t="inlineStr"/>
       <c r="N268" s="4" t="inlineStr">
         <is>
-          <t>X-MAN 2035 (pintura 2 turnos, embalaje 1) y W-MAN (capacidad de los carros)</t>
+          <t>Criterio: la ficha de seguridad del polvo ABC (W-MAN, carga de polvo: «ficha de seguridad del polvo en el puesto») indica lavar los ojos con abundante agua</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>PU-V2T.2</t>
+          <t>C17-4</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Pulmón del 2.º turno: cilindros vacíos esperando el embalaje</t>
+          <t>Mesa de medición, perchero de mangas y planillas</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>M-20</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>fchp</t>
+          <t>banco</t>
         </is>
       </c>
       <c r="E269" s="5" t="n">
-        <v>63.98</v>
+        <v>38</v>
       </c>
       <c r="F269" s="5" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="G269" s="5" t="n">
-        <v>65.26000000000001</v>
+        <v>40</v>
       </c>
       <c r="H269" s="5" t="n">
-        <v>12.11</v>
+        <v>13.2</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="J269" s="5" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="K269" s="4" t="inlineStr">
         <is>
@@ -21717,24 +23992,24 @@
         </is>
       </c>
       <c r="L269" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M269" s="4" t="inlineStr"/>
       <c r="N269" s="4" t="inlineStr">
         <is>
-          <t>X-MAN 2035 (pintura 2 turnos, embalaje 1) y W-MAN (capacidad de los carros)</t>
+          <t>W-CAR 17: 2,0 × 0,8 m, al lado de la sala de pérdidas</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>PU-V3T.1</t>
+          <t>PU-TP</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Pulmón del 2.º turno: cilindros vacíos de 1 kg en cajones</t>
+          <t>Terminados pintados -&gt; carga</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
@@ -21744,26 +24019,26 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>carro_caj</t>
+          <t>fchp</t>
         </is>
       </c>
       <c r="E270" s="5" t="n">
-        <v>62.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F270" s="5" t="n">
-        <v>10.3</v>
+        <v>12.8</v>
       </c>
       <c r="G270" s="5" t="n">
-        <v>63.8</v>
+        <v>67.38</v>
       </c>
       <c r="H270" s="5" t="n">
-        <v>11.1</v>
+        <v>13.41</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="J270" s="5" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="K270" s="4" t="inlineStr">
         <is>
@@ -21776,19 +24051,19 @@
       <c r="M270" s="4" t="inlineStr"/>
       <c r="N270" s="4" t="inlineStr">
         <is>
-          <t>X-MAN 2035 y W-MAN 11 (336 cilindros de 1 kg por carro de 12 cajones)</t>
+          <t>W-MAN 19</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>PU-V3T.2</t>
+          <t>PU-T2.1</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Pulmón del 2.º turno: cilindros vacíos de 1 kg en cajones</t>
+          <t>Pulmón del 2.º turno: terminados pintados esperando la carga</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
@@ -21798,26 +24073,26 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>carro_caj</t>
+          <t>fchp</t>
         </is>
       </c>
       <c r="E271" s="5" t="n">
-        <v>63.9</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F271" s="5" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="G271" s="5" t="n">
-        <v>65.09999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="H271" s="5" t="n">
-        <v>11.1</v>
+        <v>11.21</v>
       </c>
       <c r="I271" s="5" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="J271" s="5" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="K271" s="4" t="inlineStr">
         <is>
@@ -21830,19 +24105,19 @@
       <c r="M271" s="4" t="inlineStr"/>
       <c r="N271" s="4" t="inlineStr">
         <is>
-          <t>X-MAN 2035 y W-MAN 11 (336 cilindros de 1 kg por carro de 12 cajones)</t>
+          <t>X-MAN 2035 (pintura 2 turnos, carga 1) y W-MAN (capacidad de los carros)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>M20-1</t>
+          <t>PU-T2.2</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Estación de big bag ABC 60 (bastidor, polipasto y transporte por vacío a la cargadora)</t>
+          <t>Pulmón del 2.º turno: terminados pintados esperando la carga</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
@@ -21852,26 +24127,26 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>tanque</t>
+          <t>fchp</t>
         </is>
       </c>
       <c r="E272" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>67.47999999999999</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>11.95</v>
+        <v>10.6</v>
       </c>
       <c r="G272" s="5" t="n">
-        <v>69.09999999999999</v>
+        <v>68.75999999999999</v>
       </c>
       <c r="H272" s="5" t="n">
-        <v>13.45</v>
+        <v>11.21</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="J272" s="5" t="n">
-        <v>1.5</v>
+        <v>0.61</v>
       </c>
       <c r="K272" s="4" t="inlineStr">
         <is>
@@ -21881,26 +24156,22 @@
       <c r="L272" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M272" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="M272" s="4" t="inlineStr"/>
       <c r="N272" s="4" t="inlineStr">
         <is>
-          <t>W-MAN, carga de polvo: estación de descarga de big bag; medida: criterio</t>
+          <t>X-MAN 2035 (pintura 2 turnos, carga 1) y W-MAN (capacidad de los carros)</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>M20-3</t>
+          <t>PU-V2T.1</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Extracción localizada de polvo de la carga</t>
+          <t>Pulmón del 2.º turno: cilindros vacíos esperando el embalaje</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
@@ -21910,26 +24181,26 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>colector10</t>
+          <t>fchp</t>
         </is>
       </c>
       <c r="E273" s="5" t="n">
-        <v>69.2</v>
+        <v>62.6</v>
       </c>
       <c r="F273" s="5" t="n">
-        <v>12.65</v>
+        <v>11.5</v>
       </c>
       <c r="G273" s="5" t="n">
-        <v>70</v>
+        <v>63.88</v>
       </c>
       <c r="H273" s="5" t="n">
-        <v>13.45</v>
+        <v>12.11</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="J273" s="5" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="K273" s="4" t="inlineStr">
         <is>
@@ -21942,19 +24213,19 @@
       <c r="M273" s="4" t="inlineStr"/>
       <c r="N273" s="4" t="inlineStr">
         <is>
-          <t>W-MAN, carga de polvo: «extracción localizada de polvo»; medida: criterio</t>
+          <t>X-MAN 2035 (pintura 2 turnos, embalaje 1) y W-MAN (capacidad de los carros)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>M20-2</t>
+          <t>PU-V2T.2</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Cargadora por vacío Yukon M-000121</t>
+          <t>Pulmón del 2.º turno: cilindros vacíos esperando el embalaje</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
@@ -21964,26 +24235,26 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>carga_polvo</t>
+          <t>fchp</t>
         </is>
       </c>
       <c r="E274" s="5" t="n">
-        <v>70.09999999999999</v>
+        <v>63.98</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="G274" s="5" t="n">
-        <v>70.72</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="H274" s="5" t="n">
-        <v>13.41</v>
+        <v>12.11</v>
       </c>
       <c r="I274" s="5" t="n">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="J274" s="5" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="K274" s="4" t="inlineStr">
         <is>
@@ -21991,24 +24262,24 @@
         </is>
       </c>
       <c r="L274" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M274" s="4" t="inlineStr"/>
       <c r="N274" s="4" t="inlineStr">
         <is>
-          <t>Ficha Yukon: 620 × 510 × 1200 mm</t>
+          <t>X-MAN 2035 (pintura 2 turnos, embalaje 1) y W-MAN (capacidad de los carros)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>M20-4</t>
+          <t>PU-V3T.1</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Balanza de verificación de 50 g con pesas patrón, picos y conos M22 y M30, caja de retorno de tapones</t>
+          <t>Pulmón del 2.º turno: cilindros vacíos de 1 kg en cajones</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
@@ -22018,26 +24289,26 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>mesa_control</t>
+          <t>carro_caj</t>
         </is>
       </c>
       <c r="E275" s="5" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="F275" s="5" t="n">
-        <v>12.85</v>
+        <v>10.3</v>
       </c>
       <c r="G275" s="5" t="n">
-        <v>72.09999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="H275" s="5" t="n">
-        <v>13.45</v>
+        <v>11.1</v>
       </c>
       <c r="I275" s="5" t="n">
         <v>1.2</v>
       </c>
       <c r="J275" s="5" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K275" s="4" t="inlineStr">
         <is>
@@ -22045,24 +24316,24 @@
         </is>
       </c>
       <c r="L275" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M275" s="4" t="inlineStr"/>
       <c r="N275" s="4" t="inlineStr">
         <is>
-          <t>W-MAN, carga de polvo: equipos y herramientas; mesa 1,2 × 0,6</t>
+          <t>X-MAN 2035 y W-MAN 11 (336 cilindros de 1 kg por carro de 12 cajones)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>PU-F1</t>
+          <t>PU-V3T.2</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Carga -&gt; ensamblaje</t>
+          <t>Pulmón del 2.º turno: cilindros vacíos de 1 kg en cajones</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
@@ -22072,26 +24343,26 @@
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>fchp</t>
+          <t>carro_caj</t>
         </is>
       </c>
       <c r="E276" s="5" t="n">
-        <v>72.25</v>
+        <v>63.9</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>12.8</v>
+        <v>10.3</v>
       </c>
       <c r="G276" s="5" t="n">
-        <v>73.53</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H276" s="5" t="n">
-        <v>13.41</v>
+        <v>11.1</v>
       </c>
       <c r="I276" s="5" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="J276" s="5" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="K276" s="4" t="inlineStr">
         <is>
@@ -22104,19 +24375,19 @@
       <c r="M276" s="4" t="inlineStr"/>
       <c r="N276" s="4" t="inlineStr">
         <is>
-          <t>W-MAN, carga y ensamblaje</t>
+          <t>X-MAN 2035 y W-MAN 11 (336 cilindros de 1 kg por carro de 12 cajones)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>M21-1</t>
+          <t>M20-1</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Mesa de ensamblaje con llave dinamométrica, soporte del cilindro y grasa de silicona</t>
+          <t>Estación de big bag ABC 60 (bastidor, polipasto y transporte por vacío a la cargadora)</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
@@ -22126,26 +24397,26 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>tanque</t>
         </is>
       </c>
       <c r="E277" s="5" t="n">
-        <v>73.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F277" s="5" t="n">
-        <v>12.85</v>
+        <v>11.95</v>
       </c>
       <c r="G277" s="5" t="n">
-        <v>74.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H277" s="5" t="n">
         <v>13.45</v>
       </c>
       <c r="I277" s="5" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J277" s="5" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="K277" s="4" t="inlineStr">
         <is>
@@ -22153,24 +24424,28 @@
         </is>
       </c>
       <c r="L277" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M277" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M277" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="N277" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 21; mesa 1,2 × 0,6</t>
+          <t>W-MAN, carga de polvo: estación de descarga de big bag; medida: criterio</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>M21-2</t>
+          <t>M20-3</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Estante de cajones: válvulas, manómetros, sifones y o-rings</t>
+          <t>Extracción localizada de polvo de la carga</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
@@ -22180,26 +24455,26 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>cajonera</t>
+          <t>colector10</t>
         </is>
       </c>
       <c r="E278" s="5" t="n">
-        <v>74.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>12.75</v>
+        <v>12.65</v>
       </c>
       <c r="G278" s="5" t="n">
-        <v>75.95</v>
+        <v>70</v>
       </c>
       <c r="H278" s="5" t="n">
-        <v>13.25</v>
+        <v>13.45</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="J278" s="5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K278" s="4" t="inlineStr">
         <is>
@@ -22212,19 +24487,19 @@
       <c r="M278" s="4" t="inlineStr"/>
       <c r="N278" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 21: «estante de cajones de cada puesto, al alcance de la mano»; medida: criterio</t>
+          <t>W-MAN, carga de polvo: «extracción localizada de polvo»; medida: criterio</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>PU-F2</t>
+          <t>M20-2</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Ensamblaje -&gt; presurización</t>
+          <t>Cargadora por vacío Yukon M-000121</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
@@ -22234,26 +24509,26 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>fchp</t>
+          <t>carga_polvo</t>
         </is>
       </c>
       <c r="E279" s="5" t="n">
-        <v>75.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F279" s="5" t="n">
-        <v>10.85</v>
+        <v>12.9</v>
       </c>
       <c r="G279" s="5" t="n">
-        <v>75.91</v>
+        <v>70.72</v>
       </c>
       <c r="H279" s="5" t="n">
-        <v>12.13</v>
+        <v>13.41</v>
       </c>
       <c r="I279" s="5" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J279" s="5" t="n">
-        <v>1.28</v>
+        <v>0.51</v>
       </c>
       <c r="K279" s="4" t="inlineStr">
         <is>
@@ -22261,24 +24536,24 @@
         </is>
       </c>
       <c r="L279" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M279" s="4" t="inlineStr"/>
       <c r="N279" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 21 y 22</t>
+          <t>Ficha Yukon: 620 × 510 × 1200 mm</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>M22-1</t>
+          <t>M20-4</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Pinza Yukon M-000150 sobre mesa (N₂ por cañería desde la jaula exterior, regulador con alivio)</t>
+          <t>Balanza de verificación de 50 g con pesas patrón, picos y conos M22 y M30, caja de retorno de tapones</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
@@ -22288,30 +24563,30 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>presurizacion</t>
+          <t>mesa_control</t>
         </is>
       </c>
       <c r="E280" s="5" t="n">
-        <v>75.34999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>12.85</v>
       </c>
       <c r="G280" s="5" t="n">
-        <v>75.95</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H280" s="5" t="n">
-        <v>10.4</v>
+        <v>13.45</v>
       </c>
       <c r="I280" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J280" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="J280" s="5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K280" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L280" s="4" t="n">
@@ -22320,19 +24595,19 @@
       <c r="M280" s="4" t="inlineStr"/>
       <c r="N280" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 22; mesa 1,2 × 0,6</t>
+          <t>W-MAN, carga de polvo: equipos y herramientas; mesa 1,2 × 0,6</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>PU-F3</t>
+          <t>LO-1</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Presurización -&gt; pérdidas</t>
+          <t>Lavaojos de emergencia de la carga de polvo de manuales</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
@@ -22342,30 +24617,30 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>fchp</t>
+          <t>lavaojos</t>
         </is>
       </c>
       <c r="E281" s="5" t="n">
-        <v>72.90000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="F281" s="5" t="n">
-        <v>8.65</v>
+        <v>11.35</v>
       </c>
       <c r="G281" s="5" t="n">
-        <v>74.18000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="H281" s="5" t="n">
-        <v>9.26</v>
+        <v>11.95</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>1.28</v>
+        <v>0.6</v>
       </c>
       <c r="J281" s="5" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="K281" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L281" s="4" t="n">
@@ -22374,19 +24649,19 @@
       <c r="M281" s="4" t="inlineStr"/>
       <c r="N281" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 22 y 23</t>
+          <t>Criterio: la ficha de seguridad del polvo ABC (W-MAN, carga de polvo: «ficha de seguridad del polvo en el puesto») indica lavar los ojos con abundante agua</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>M23-1</t>
+          <t>PU-F1</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>Tanque de inmersión inoxidable Firesafer FS-SS100 (iluminación, estante sumergido, temporizador)</t>
+          <t>Carga -&gt; ensamblaje</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
@@ -22396,51 +24671,51 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>hermeticidad</t>
+          <t>fchp</t>
         </is>
       </c>
       <c r="E282" s="5" t="n">
-        <v>73.90000000000001</v>
+        <v>72.25</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>6.3</v>
+        <v>12.8</v>
       </c>
       <c r="G282" s="5" t="n">
-        <v>75.7</v>
+        <v>73.53</v>
       </c>
       <c r="H282" s="5" t="n">
-        <v>7.3</v>
+        <v>13.41</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="J282" s="5" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="K282" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L282" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M282" s="4" t="inlineStr"/>
       <c r="N282" s="4" t="inlineStr">
         <is>
-          <t>Catálogo Filling Line, pág. 44: 1000 × 1800 × 900 mm</t>
+          <t>W-MAN, carga y ensamblaje</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>M23-2</t>
+          <t>M21-1</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Cajón de rechazos con tarjeta roja (punto de la pérdida anotado)</t>
+          <t>Mesa de ensamblaje con llave dinamométrica, soporte del cilindro y grasa de silicona</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
@@ -22450,51 +24725,51 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>rechazo</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E283" s="5" t="n">
-        <v>73.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F283" s="5" t="n">
-        <v>6.35</v>
+        <v>12.85</v>
       </c>
       <c r="G283" s="5" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="H283" s="5" t="n">
-        <v>6.75</v>
+        <v>13.45</v>
       </c>
       <c r="I283" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J283" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="J283" s="5" t="n">
-        <v>0.4</v>
-      </c>
       <c r="K283" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L283" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M283" s="4" t="inlineStr"/>
       <c r="N283" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 23: «al cajón identificado con tarjeta roja al lado del tanque»; cajón de 600 × 400 mm</t>
+          <t>W-MAN 21; mesa 1,2 × 0,6</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>PU-F4</t>
+          <t>M21-2</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Pérdidas -&gt; etiquetado</t>
+          <t>Estante de cajones: válvulas, manómetros, sifones y o-rings</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
@@ -22504,26 +24779,26 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>fchp</t>
+          <t>cajonera</t>
         </is>
       </c>
       <c r="E284" s="5" t="n">
-        <v>71.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>6.35</v>
+        <v>12.75</v>
       </c>
       <c r="G284" s="5" t="n">
-        <v>72.98</v>
+        <v>75.95</v>
       </c>
       <c r="H284" s="5" t="n">
-        <v>6.96</v>
+        <v>13.25</v>
       </c>
       <c r="I284" s="5" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="J284" s="5" t="n">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="K284" s="4" t="inlineStr">
         <is>
@@ -22536,19 +24811,19 @@
       <c r="M284" s="4" t="inlineStr"/>
       <c r="N284" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 23 y 24</t>
+          <t>W-MAN 21: «estante de cajones de cada puesto, al alcance de la mano»; medida: criterio</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>M24-1</t>
+          <t>PU-F2</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Dispensador de etiquetas, posicionador por formato y Zebra ZD421 sobre mesa</t>
+          <t>Ensamblaje -&gt; presurización</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
@@ -22558,51 +24833,51 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>etiquetadora</t>
+          <t>fchp</t>
         </is>
       </c>
       <c r="E285" s="5" t="n">
-        <v>70.3</v>
+        <v>75.3</v>
       </c>
       <c r="F285" s="5" t="n">
-        <v>6.35</v>
+        <v>10.85</v>
       </c>
       <c r="G285" s="5" t="n">
-        <v>71.5</v>
+        <v>75.91</v>
       </c>
       <c r="H285" s="5" t="n">
-        <v>6.95</v>
+        <v>12.13</v>
       </c>
       <c r="I285" s="5" t="n">
-        <v>1.2</v>
+        <v>0.61</v>
       </c>
       <c r="J285" s="5" t="n">
-        <v>0.6</v>
+        <v>1.28</v>
       </c>
       <c r="K285" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L285" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M285" s="4" t="inlineStr"/>
       <c r="N285" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 24; mesa 1,2 × 0,6</t>
+          <t>W-MAN 21 y 22</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>M24-2</t>
+          <t>M22-1</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Estante del puesto: etiquetas preimpresas por formato, rollos de la impresora y paños</t>
+          <t>Pinza Yukon M-000150 sobre mesa (N₂ por cañería desde la jaula exterior, regulador con alivio)</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
@@ -22612,51 +24887,51 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>cajonera</t>
+          <t>presurizacion</t>
         </is>
       </c>
       <c r="E286" s="5" t="n">
-        <v>69.59999999999999</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>6.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G286" s="5" t="n">
-        <v>70.2</v>
+        <v>75.95</v>
       </c>
       <c r="H286" s="5" t="n">
-        <v>7.2</v>
+        <v>10.4</v>
       </c>
       <c r="I286" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="J286" s="5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K286" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L286" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M286" s="4" t="inlineStr"/>
       <c r="N286" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 24: «los deja en el estante del puesto»; medida: criterio</t>
+          <t>W-MAN 22; mesa 1,2 × 0,6</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>PU-F5</t>
+          <t>PU-F3</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Etiquetado -&gt; embalaje</t>
+          <t>Presurización -&gt; pérdidas</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
@@ -22670,16 +24945,16 @@
         </is>
       </c>
       <c r="E287" s="5" t="n">
-        <v>68.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F287" s="5" t="n">
-        <v>6.35</v>
+        <v>8.65</v>
       </c>
       <c r="G287" s="5" t="n">
-        <v>69.48</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="H287" s="5" t="n">
-        <v>6.96</v>
+        <v>9.26</v>
       </c>
       <c r="I287" s="5" t="n">
         <v>1.28</v>
@@ -22698,19 +24973,19 @@
       <c r="M287" s="4" t="inlineStr"/>
       <c r="N287" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 24 y 25</t>
+          <t>W-MAN 22 y 23</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>M25-1</t>
+          <t>M23-1</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Mesa de encajonado (terminados)</t>
+          <t>Tanque de inmersión inoxidable Firesafer FS-SS100 (iluminación, estante sumergido, temporizador)</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
@@ -22720,26 +24995,26 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>palletizado</t>
+          <t>hermeticidad</t>
         </is>
       </c>
       <c r="E288" s="5" t="n">
-        <v>63.6</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>7.85</v>
+        <v>6.3</v>
       </c>
       <c r="G288" s="5" t="n">
-        <v>64.8</v>
+        <v>75.7</v>
       </c>
       <c r="H288" s="5" t="n">
-        <v>8.449999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J288" s="5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K288" s="4" t="inlineStr">
         <is>
@@ -22752,19 +25027,19 @@
       <c r="M288" s="4" t="inlineStr"/>
       <c r="N288" s="4" t="inlineStr">
         <is>
-          <t>X-MAN: 2 puestos; mesa 1,2 × 0,6</t>
+          <t>Catálogo Filling Line, pág. 44: 1000 × 1800 × 900 mm</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>M25-2</t>
+          <t>M23-2</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Mesa de encajonado (cilindros vacíos, con protocolo de ensayo)</t>
+          <t>Cajón de rechazos con tarjeta roja (punto de la pérdida anotado)</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
@@ -22774,26 +25049,26 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>palletizado</t>
+          <t>rechazo</t>
         </is>
       </c>
       <c r="E289" s="5" t="n">
-        <v>64.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="F289" s="5" t="n">
-        <v>7.85</v>
+        <v>6.35</v>
       </c>
       <c r="G289" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="H289" s="5" t="n">
-        <v>8.449999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J289" s="5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K289" s="4" t="inlineStr">
         <is>
@@ -22801,24 +25076,24 @@
         </is>
       </c>
       <c r="L289" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M289" s="4" t="inlineStr"/>
       <c r="N289" s="4" t="inlineStr">
         <is>
-          <t>X-MAN: 2 puestos; mesa 1,2 × 0,6; W-MAN 25</t>
+          <t>W-MAN 23: «al cajón identificado con tarjeta roja al lado del tanque»; cajón de 600 × 400 mm</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>M25-3</t>
+          <t>PU-F4</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Armadora automática de cajas (regulada para la caja del 1 kg)</t>
+          <t>Pérdidas -&gt; etiquetado</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
@@ -22828,30 +25103,30 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>palletizado</t>
+          <t>fchp</t>
         </is>
       </c>
       <c r="E290" s="5" t="n">
-        <v>63.6</v>
+        <v>71.7</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="G290" s="5" t="n">
-        <v>65.62</v>
+        <v>72.98</v>
       </c>
       <c r="H290" s="5" t="n">
-        <v>7.67</v>
+        <v>6.96</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>2.02</v>
+        <v>1.28</v>
       </c>
       <c r="J290" s="5" t="n">
-        <v>1.42</v>
+        <v>0.61</v>
       </c>
       <c r="K290" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L290" s="4" t="n">
@@ -22860,19 +25135,19 @@
       <c r="M290" s="4" t="inlineStr"/>
       <c r="N290" s="4" t="inlineStr">
         <is>
-          <t>Sin cotizar; referencia FS-DDP50: 2020 × 1420 mm</t>
+          <t>W-MAN 23 y 24</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>M25-4</t>
+          <t>M24-1</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Envolvedora EDOS PS5 (pallet listo para el autoelevador, sobre la entrega del rack B)</t>
+          <t>Dispensador de etiquetas, posicionador por formato y Zebra ZD421 sobre mesa</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
@@ -22882,26 +25157,26 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>envolvedora</t>
+          <t>etiquetadora</t>
         </is>
       </c>
       <c r="E291" s="5" t="n">
-        <v>60.85</v>
+        <v>70.3</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="G291" s="5" t="n">
-        <v>63.4</v>
+        <v>71.5</v>
       </c>
       <c r="H291" s="5" t="n">
-        <v>7.75</v>
+        <v>6.95</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>2.55</v>
+        <v>1.2</v>
       </c>
       <c r="J291" s="5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="K291" s="4" t="inlineStr">
         <is>
@@ -22909,28 +25184,24 @@
         </is>
       </c>
       <c r="L291" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M291" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M291" s="4" t="inlineStr"/>
       <c r="N291" s="4" t="inlineStr">
         <is>
-          <t>Plano de cotas EDOS 26880: 2550 × 1500 mm</t>
+          <t>W-MAN 24; mesa 1,2 × 0,6</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>M25-5</t>
+          <t>M24-2</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Pila de pallets vacíos 1200 × 1000 (junto a la envolvedora)</t>
+          <t>Estante del puesto: etiquetas preimpresas por formato, rollos de la impresora y paños</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
@@ -22940,30 +25211,30 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>pallets_q</t>
+          <t>cajonera</t>
         </is>
       </c>
       <c r="E292" s="5" t="n">
-        <v>60.85</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>7.95</v>
+        <v>6.3</v>
       </c>
       <c r="G292" s="5" t="n">
-        <v>62.05</v>
+        <v>70.2</v>
       </c>
       <c r="H292" s="5" t="n">
-        <v>8.949999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J292" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K292" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L292" s="4" t="n">
@@ -22972,19 +25243,19 @@
       <c r="M292" s="4" t="inlineStr"/>
       <c r="N292" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 25</t>
+          <t>W-MAN 24: «los deja en el estante del puesto»; medida: criterio</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>M25-8</t>
+          <t>PU-F5</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Pallet en armado sobre el piso, al lado de las mesas</t>
+          <t>Etiquetado -&gt; embalaje</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
@@ -22994,26 +25265,26 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>pallets_q</t>
+          <t>fchp</t>
         </is>
       </c>
       <c r="E293" s="5" t="n">
-        <v>62.2</v>
+        <v>68.2</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>7.95</v>
+        <v>6.35</v>
       </c>
       <c r="G293" s="5" t="n">
-        <v>63.4</v>
+        <v>69.48</v>
       </c>
       <c r="H293" s="5" t="n">
-        <v>8.949999999999999</v>
+        <v>6.96</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="J293" s="5" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="K293" s="4" t="inlineStr">
         <is>
@@ -23026,19 +25297,19 @@
       <c r="M293" s="4" t="inlineStr"/>
       <c r="N293" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 25: «apilar las cajas sobre el pallet según el plano de armado»</t>
+          <t>W-MAN 24 y 25</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>M25-6</t>
+          <t>M25-1</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Pallet de cajas plegadas (al lado de la armadora)</t>
+          <t>Mesa de encajonado (terminados)</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
@@ -23048,26 +25319,26 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>pallets_q</t>
+          <t>palletizado</t>
         </is>
       </c>
       <c r="E294" s="5" t="n">
-        <v>65.8</v>
+        <v>63.6</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>6.25</v>
+        <v>7.85</v>
       </c>
       <c r="G294" s="5" t="n">
-        <v>67</v>
+        <v>64.8</v>
       </c>
       <c r="H294" s="5" t="n">
-        <v>7.18</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I294" s="5" t="n">
         <v>1.2</v>
       </c>
       <c r="J294" s="5" t="n">
-        <v>0.93</v>
+        <v>0.6</v>
       </c>
       <c r="K294" s="4" t="inlineStr">
         <is>
@@ -23075,24 +25346,24 @@
         </is>
       </c>
       <c r="L294" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M294" s="4" t="inlineStr"/>
       <c r="N294" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 25: las cajas llegan plegadas en pallets desde el almacén</t>
+          <t>X-MAN: 2 puestos; mesa 1,2 × 0,6</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>M25-7</t>
+          <t>M25-2</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Lugar de las transpaletas eléctrica y manual (demarcado)</t>
+          <t>Mesa de encajonado (cilindros vacíos, con protocolo de ensayo)</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
@@ -23102,51 +25373,51 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>transpaleta</t>
+          <t>palletizado</t>
         </is>
       </c>
       <c r="E295" s="5" t="n">
-        <v>60.85</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F295" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="G295" s="5" t="n">
-        <v>62.35</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H295" s="5" t="n">
-        <v>11.3</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J295" s="5" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="K295" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L295" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M295" s="4" t="inlineStr"/>
       <c r="N295" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 25: transpaleta eléctrica y transpaleta manual de respaldo; 0,7 × 1,6 m cada una (criterio)</t>
+          <t>X-MAN: 2 puestos; mesa 1,2 × 0,6; W-MAN 25</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>M25-9</t>
+          <t>M25-3</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Estante de film, etiquetas de caja y de pallet, protocolos y cúter</t>
+          <t>Armadora automática de cajas (regulada para la caja del 1 kg)</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
@@ -23156,26 +25427,26 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>estanteria</t>
+          <t>palletizado</t>
         </is>
       </c>
       <c r="E296" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>8.1</v>
+        <v>6.25</v>
       </c>
       <c r="G296" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>65.62</v>
       </c>
       <c r="H296" s="5" t="n">
-        <v>8.6</v>
+        <v>7.67</v>
       </c>
       <c r="I296" s="5" t="n">
-        <v>1.2</v>
+        <v>2.02</v>
       </c>
       <c r="J296" s="5" t="n">
-        <v>0.5</v>
+        <v>1.42</v>
       </c>
       <c r="K296" s="4" t="inlineStr">
         <is>
@@ -23188,48 +25459,48 @@
       <c r="M296" s="4" t="inlineStr"/>
       <c r="N296" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 25: materiales de embalaje que trae el operario de almacén</t>
+          <t>Sin cotizar; referencia FS-DDP50: 2020 × 1420 mm</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>PTM-1</t>
+          <t>M25-4</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Rack de PT de manuales: terminados y revendidos (5 módulos de 2,65 m × 5 niveles × 2 pallets = 50 posiciones)</t>
+          <t>Envolvedora EDOS PS5 (pallet listo para el autoelevador, sobre la entrega del rack B)</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>PT-M</t>
+          <t>M-20</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>rack</t>
+          <t>envolvedora</t>
         </is>
       </c>
       <c r="E297" s="5" t="n">
-        <v>60.75</v>
+        <v>60.85</v>
       </c>
       <c r="F297" s="5" t="n">
-        <v>0.25</v>
+        <v>6.25</v>
       </c>
       <c r="G297" s="5" t="n">
-        <v>74</v>
+        <v>63.4</v>
       </c>
       <c r="H297" s="5" t="n">
-        <v>1.35</v>
+        <v>7.75</v>
       </c>
       <c r="I297" s="5" t="n">
-        <v>13.25</v>
+        <v>2.55</v>
       </c>
       <c r="J297" s="5" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="K297" s="4" t="inlineStr">
         <is>
@@ -23246,48 +25517,48 @@
       </c>
       <c r="N297" s="4" t="inlineStr">
         <is>
-          <t>W-MAN 25: rack de PT y de cilindros en el mismo almacén, el autoelevador ubica el pallet en altura o lo carga directo al camión (P4); 70 pallets (semana 40 + diciembre 30) + 17 de revendidos (X-ALM) en 90 posiciones</t>
+          <t>Plano de cotas EDOS 26880: 2550 × 1500 mm</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>PTM-2</t>
+          <t>M25-5</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Rack de PT de manuales: cilindros vacíos (4 módulos de 2,65 m × 5 niveles × 2 pallets = 40 posiciones)</t>
+          <t>Pila de pallets vacíos 1200 × 1000 (junto a la envolvedora)</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>PT-M2</t>
+          <t>M-20</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>rack</t>
+          <t>pallets_q</t>
         </is>
       </c>
       <c r="E298" s="5" t="n">
-        <v>65.40000000000001</v>
+        <v>60.85</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>5.05</v>
+        <v>7.95</v>
       </c>
       <c r="G298" s="5" t="n">
-        <v>76</v>
+        <v>62.05</v>
       </c>
       <c r="H298" s="5" t="n">
-        <v>6.15</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I298" s="5" t="n">
-        <v>10.6</v>
+        <v>1.2</v>
       </c>
       <c r="J298" s="5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K298" s="4" t="inlineStr">
         <is>
@@ -23297,12 +25568,340 @@
       <c r="L298" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M298" s="4" t="inlineStr">
+      <c r="M298" s="4" t="inlineStr"/>
+      <c r="N298" s="4" t="inlineStr">
+        <is>
+          <t>W-MAN 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>M25-8</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>Pallet en armado sobre el piso, al lado de las mesas</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>M-20</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr">
+        <is>
+          <t>pallets_q</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="F299" s="5" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="G299" s="5" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="H299" s="5" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="I299" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J299" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K299" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L299" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M299" s="4" t="inlineStr"/>
+      <c r="N299" s="4" t="inlineStr">
+        <is>
+          <t>W-MAN 25: «apilar las cajas sobre el pallet según el plano de armado»</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>M25-6</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>Pallet de cajas plegadas (al lado de la armadora)</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>M-20</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>pallets_q</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="F300" s="5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="G300" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="H300" s="5" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="I300" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J300" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K300" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L300" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" s="4" t="inlineStr"/>
+      <c r="N300" s="4" t="inlineStr">
+        <is>
+          <t>W-MAN 25: las cajas llegan plegadas en pallets desde el almacén</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>M25-7</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>Lugar de las transpaletas eléctrica y manual (demarcado)</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>M-20</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>transpaleta</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="F301" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G301" s="5" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="H301" s="5" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I301" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J301" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K301" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L301" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" s="4" t="inlineStr"/>
+      <c r="N301" s="4" t="inlineStr">
+        <is>
+          <t>W-MAN 25: transpaleta eléctrica y transpaleta manual de respaldo; 0,7 × 1,6 m cada una (criterio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>M25-9</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>Estante de film, etiquetas de caja y de pallet, protocolos y cúter</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>M-20</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
+        <is>
+          <t>estanteria</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="F302" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G302" s="5" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="H302" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I302" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J302" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K302" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L302" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" s="4" t="inlineStr"/>
+      <c r="N302" s="4" t="inlineStr">
+        <is>
+          <t>W-MAN 25: materiales de embalaje que trae el operario de almacén</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>PTM-1</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>Rack de PT de manuales: terminados y revendidos (5 módulos de 2,65 m × 5 niveles × 2 pallets = 50 posiciones)</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>PT-M</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="F303" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G303" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="H303" s="5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I303" s="5" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="J303" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K303" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L303" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M303" s="4" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="N298" s="4" t="inlineStr">
+      <c r="N303" s="4" t="inlineStr">
+        <is>
+          <t>W-MAN 25: rack de PT y de cilindros en el mismo almacén, el autoelevador ubica el pallet en altura o lo carga directo al camión (P4); 70 pallets (semana 40 + diciembre 30) + 17 de revendidos (X-ALM) en 90 posiciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>PTM-2</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>Rack de PT de manuales: cilindros vacíos (4 módulos de 2,65 m × 5 niveles × 2 pallets = 40 posiciones)</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>PT-M2</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="F304" s="5" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="G304" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="H304" s="5" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I304" s="5" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J304" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K304" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L304" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M304" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N304" s="4" t="inlineStr">
         <is>
           <t>W-MAN 25: rack de PT y de cilindros en el mismo almacén, el autoelevador ubica el pallet en altura o lo carga directo al camión (P4); 70 pallets (semana 40 + diciembre 30) + 17 de revendidos (X-ALM) en 90 posiciones</t>
         </is>
@@ -23567,7 +26166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23920,10 +26519,10 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>32</v>
+        <v>28.6</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>33.2</v>
+        <v>29.8</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>1.2</v>
@@ -23938,82 +26537,82 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Salida de la banda sur (reserva y ensayos de lote)</t>
+          <t>Salida de la banda sur (ensayos de lote y servicios)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>PN-1</t>
+          <t>PE-5</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Este</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>35.55</v>
+        <v>18.75</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>36.35</v>
+        <v>19.95</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>peatonal</t>
+          <t>emergencia</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Sala técnica: puerta directa a la planta</t>
+          <t>Salida del extremo este de la senda del pasillo principal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>PN-2</t>
+          <t>PE-6</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Este</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>46.7</v>
+        <v>7.45</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>47.55</v>
+        <v>8.65</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>peatonal</t>
+          <t>emergencia</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Comedor (almuerzo: cruce, lavamanos, comedor)</t>
+          <t>Salida de la terminación de manuales</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>PN-3</t>
+          <t>PE-7</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -24022,23 +26621,227 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>57.4</v>
+        <v>13.85</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>58.9</v>
+        <v>14.95</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
+          <t>emergencia</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Salida del extremo oeste de la senda norte (almacén y manuales)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>PE-8</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>emergencia</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Salida del extremo este de la senda norte (detección, cuelgue y pintura)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>PE-9</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>emergencia</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Salida del depósito de PT de manuales</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>servicio</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Retiro de residuos especiales por el gestor (doble hoja)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>PN-1</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
           <t>peatonal</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Sala técnica: puerta directa a la planta</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PN-2</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>peatonal</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Comedor (almuerzo: cruce, lavamanos, comedor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>PN-3</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>peatonal</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Paso de personal a la planta (doble hoja)</t>
         </is>
@@ -24539,410 +27342,294 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Alturas usadas en los cortes (FL_PI10_06)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Elemento</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Alto (m)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Fuente</t>
+          <t>Salidas de la nave y recorrido de escape (Dec. 351/79, anexo VII)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>N = 224 personas (3572 m² / 16 m²), 3 unidades de ancho, ancho mínimo 1.55 m; recorrido máximo 38.0 m (criterio 40 m) por la línea de libre trayectoria.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>M4-3</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>ET Sangiacomo T 63R: 2790 mm</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Salida</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Muro</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ancho (m)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>m² que llegan</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Uso</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>M3-2</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Cotización Leapion: 1200 mm</t>
+      <c r="D5" s="5" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Patio de ensayos de lote (17): la muestra sale a la rodadura</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>M8-1</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Catálogo Firesafer FS-RM01: 1250 mm</t>
+          <t>PE-1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>369.2</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Salida del ángulo SO (extremo de la senda de los locales)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>M9-1</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>ET Getweld ZF-500 (referencia): 1600 mm</t>
+          <t>PE-3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Salida del almacén (extremo norte del pasillo AL-B)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>M7-1</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Catálogo Firesafer FS-HFM1: 1580 mm</t>
+          <t>PE-4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Salida de la banda sur (ensayos de lote y servicios)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>M10-1</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>ET Del Fabro: 1800 mm</t>
+          <t>PE-5</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>278.5</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Salida del extremo este de la senda del pasillo principal</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>M11-1</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Presupuesto Pilman SWM-400: 1280 mm</t>
+          <t>PE-6</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Salida de la terminación de manuales</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>M14-*</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Catálogo Firesafer FS-JD12A: 1350 mm</t>
+          <t>PE-7</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>521.8</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Salida del extremo oeste de la senda norte (almacén y manuales)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>M15-*</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>ET secadora Yukon: 1750 mm</t>
+          <t>PE-8</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>457.8</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Salida del extremo este de la senda norte (detección, cuelgue y pintura)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>M16-1</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Cotización Airblast G-100: 2200 mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>M19-1</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>ET línea Firesafer: 25 × 8 × 4 m</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>M20-2</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
+          <t>PE-9</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Ficha Yukon M-000121: 1200 mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>M23-1</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Catálogo Filling Line FS-SS100: 900 mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>C17-2</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>W-CAR 17: recinto de 3 m de alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>C13-3</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>W-CAR 13: bastidor de 2,8 m</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>RC-*</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>W-CAR 1 tabla 5: racks de carros de ≈ 3 m</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>R1-*</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
+      <c r="D13" s="5" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Criterio: la carga de arriba llega a la elevación máxima del Heli CPCD50, 6 m (W-CAR 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>PTM-*</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Criterio: 5 niveles hasta la elevación máxima del Heli CPCD50, 6 m (W-CAR 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>PQ-*</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>W-CAR 1: big bag de 1,2 m de alto, apilado de a 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>filas</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Hoja de especificaciones «Polvos carros»: carro de 50 kg, 1160 mm (25 kg 1085; 100 kg 1360)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>rodantes</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Hoja de especificaciones «Polvos carros»: carro de 50 kg, 1160 mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>lugar</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Hoja de especificaciones «Polvos carros»: carro de 50 kg, 1160 mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>banco</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>W-CAR 1: mesa de trabajo metálica de unos 86 cm de alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>mesa_control</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>W-CAR 1: mesa de 86 cm</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>inspeccion</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>W-CAR 1: mesa de 86 cm</t>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Salida del depósito de PT de manuales</t>
         </is>
       </c>
     </row>
